--- a/AAII_Financials/Quarterly/LESL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LESL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
   <si>
     <t>LESL</t>
   </si>
@@ -656,296 +656,321 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F7" s="2">
         <v>45108</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45017</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>44835</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>44744</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44653</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44562</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44471</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44380</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44289</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44198</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44009</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43918</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43827</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43736</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43645</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43554</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43463</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>174000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>432400</v>
+      </c>
+      <c r="F8" s="3">
         <v>610900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>212800</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>195100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>475600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>673600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>228100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>184800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>408900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>596500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>192400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>145000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>381300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>479900</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="3">
         <v>123000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>298200</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>123600</v>
+      </c>
+      <c r="E9" s="3">
+        <v>272200</v>
+      </c>
+      <c r="F9" s="3">
         <v>359300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>141700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>129800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>258400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>370000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>142400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>117500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>220900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>312800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>120800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>93300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>214700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>269200</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3">
         <v>81900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>166900</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>50400</v>
+      </c>
+      <c r="E10" s="3">
+        <v>160200</v>
+      </c>
+      <c r="F10" s="3">
         <v>251600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>71100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>65300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>217200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>303600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>85700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>67300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>188000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>283700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>71600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>51700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>166600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>210700</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3">
         <v>41100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>131300</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -969,8 +994,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1034,8 +1061,14 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1099,26 +1132,32 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>2300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>4200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>3500</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
@@ -1126,46 +1165,52 @@
         <v>0</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>6400</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>1900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>7300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>2300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R14" s="3">
-        <v>0</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1229,8 +1274,14 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1251,138 +1302,152 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>210400</v>
+      </c>
+      <c r="E17" s="3">
+        <v>393800</v>
+      </c>
+      <c r="F17" s="3">
         <v>495100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>238000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>222100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>392500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>501500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>232100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>197300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>341800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>430100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>193000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>178100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>313300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>368300</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3">
         <v>141600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>239300</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-36400</v>
+      </c>
+      <c r="E18" s="3">
+        <v>38600</v>
+      </c>
+      <c r="F18" s="3">
         <v>115800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-25200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-27000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>83100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>172100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-4000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-12500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>67100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>166400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-33100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>68000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>111600</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3">
         <v>-18600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>58900</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1406,8 +1471,10 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1424,315 +1491,345 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3">
         <v>200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-1000</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-600</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-3000</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-28100</v>
+      </c>
+      <c r="E21" s="3">
+        <v>47100</v>
+      </c>
+      <c r="F21" s="3">
         <v>124000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-16300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-18500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>91000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>179300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>2400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>74000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>171900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>4600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-26500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>76200</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S21" s="3">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U21" s="3">
         <v>86300</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>17700</v>
+        <v>17100</v>
       </c>
       <c r="E22" s="3">
         <v>17200</v>
       </c>
       <c r="F22" s="3">
+        <v>17700</v>
+      </c>
+      <c r="G22" s="3">
+        <v>17200</v>
+      </c>
+      <c r="H22" s="3">
         <v>13400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>9600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>6800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>6900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>6900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>7400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>7400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>8100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>11500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>18600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>19500</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T22" s="3">
         <v>22400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>23900</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-53500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>21400</v>
+      </c>
+      <c r="F23" s="3">
         <v>98100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-42400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-40300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>73500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>165400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-11100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-19700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>59300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>158200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-9800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-44600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>49300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>91500</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3">
         <v>-41200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>32000</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>4900</v>
+      </c>
+      <c r="F24" s="3">
         <v>25600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-10900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-10100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>15600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>42400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-3700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-5300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>14700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>39400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-3300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-14300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>7200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>19600</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T24" s="3">
         <v>-15000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>31200</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1796,138 +1893,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-39600</v>
+      </c>
+      <c r="E26" s="3">
+        <v>16500</v>
+      </c>
+      <c r="F26" s="3">
         <v>72500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-31500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-30300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>57900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>123000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-7400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-14500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>44500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>118800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-6500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-30300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>42100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>71900</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3">
         <v>-26200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>800</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-39600</v>
+      </c>
+      <c r="E27" s="3">
+        <v>16500</v>
+      </c>
+      <c r="F27" s="3">
         <v>72500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-31500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-30300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>57900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>123000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-7400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-14500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>44500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>118800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-6500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-30300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>42100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>71900</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3">
         <v>-26200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>800</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1991,8 +2106,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2056,8 +2177,14 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2121,8 +2248,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2186,8 +2319,14 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2204,120 +2343,132 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
+        <v>0</v>
+      </c>
+      <c r="J32" s="3">
         <v>-200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>1000</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>600</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>3000</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-39600</v>
+      </c>
+      <c r="E33" s="3">
+        <v>16500</v>
+      </c>
+      <c r="F33" s="3">
         <v>72500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-31500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-30300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>57900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>123000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-7400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-14500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>44500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>118800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-6500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-30300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>42100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>71900</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3">
         <v>-26200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>800</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2381,143 +2532,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-39600</v>
+      </c>
+      <c r="E35" s="3">
+        <v>16500</v>
+      </c>
+      <c r="F35" s="3">
         <v>72500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-31500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-30300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>57900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>123000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-7400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-14500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>44500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>118800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-6500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-30300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>42100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>71900</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3">
         <v>-26200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>800</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F38" s="2">
         <v>45108</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45017</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>44835</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>44744</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44653</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44562</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44471</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44380</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44289</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44198</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44009</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43918</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43827</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43736</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43645</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43554</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43463</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2541,8 +2710,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2566,56 +2737,58 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E41" s="3">
+        <v>55400</v>
+      </c>
+      <c r="F41" s="3">
         <v>19400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>8700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>112300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>193100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>52000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>53300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>343500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>309100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>88700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>102800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>157100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>148900</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2631,8 +2804,14 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2696,56 +2875,62 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>22500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>29400</v>
+      </c>
+      <c r="F43" s="3">
         <v>49300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>38000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>46400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>45300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>47300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>44200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>39400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>77700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>47800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>94500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>74200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>31500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>35800</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2761,56 +2946,62 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>334000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>311800</v>
+      </c>
+      <c r="F44" s="3">
         <v>436600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>492300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>429500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>361700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>361400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>345000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>244600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>198800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>224500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>277900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>174500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>149000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>181100</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2826,56 +3017,62 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>23600</v>
+      </c>
+      <c r="F45" s="3">
         <v>31500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>52700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>29900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>23100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>30500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>30700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>38200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>41100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>28600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>87300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>65500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>22700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>24600</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2891,56 +3088,62 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>392000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>420300</v>
+      </c>
+      <c r="F46" s="3">
         <v>536700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>591700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>508500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>542400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>632300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>471900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>375500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>601700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>610100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>448300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>340100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>360200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>390400</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2956,8 +3159,14 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3021,56 +3230,62 @@
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>330700</v>
+      </c>
+      <c r="E48" s="3">
+        <v>341700</v>
+      </c>
+      <c r="F48" s="3">
         <v>335800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>312000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>308900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>314600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>293300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>279100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>273200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>282600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>235400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>245200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>253800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>244000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>74700</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3086,56 +3301,62 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>217900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>218900</v>
+      </c>
+      <c r="F49" s="3">
         <v>219800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>216600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>218100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>213700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>155700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>146900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>132400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>129000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>127700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>128600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>121200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>122000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>121700</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3151,8 +3372,14 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3216,8 +3443,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3281,56 +3514,62 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>57900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>53500</v>
+      </c>
+      <c r="F52" s="3">
         <v>45100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>42900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>41300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>39000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>35700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>32400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>30200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>28900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>24600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>35900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>31400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>21000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1200</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3346,8 +3585,14 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3411,56 +3656,62 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>998500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1034400</v>
+      </c>
+      <c r="F54" s="3">
         <v>1137400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1163200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1076800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1109600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1117000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>930200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>811300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1042200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>997800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>857300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>745800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>746400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>588000</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3476,8 +3727,14 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3501,8 +3758,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3526,56 +3785,58 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>63500</v>
+      </c>
+      <c r="E57" s="3">
+        <v>58600</v>
+      </c>
+      <c r="F57" s="3">
         <v>147400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>139800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>117300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>156500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>219000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>160900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>99500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>101000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>155500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>181500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>69000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>92400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>133100</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3591,8 +3852,14 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3627,19 +3894,19 @@
         <v>8100</v>
       </c>
       <c r="N58" s="3">
-        <v>8300</v>
+        <v>8100</v>
       </c>
       <c r="O58" s="3">
-        <v>8300</v>
+        <v>8100</v>
       </c>
       <c r="P58" s="3">
         <v>8300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>3</v>
+      <c r="Q58" s="3">
+        <v>8300</v>
+      </c>
+      <c r="R58" s="3">
+        <v>8300</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>3</v>
@@ -3656,56 +3923,62 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>132900</v>
+      </c>
+      <c r="E59" s="3">
+        <v>159200</v>
+      </c>
+      <c r="F59" s="3">
         <v>159800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>144500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>129200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>183400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>205800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>169200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>146600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>200700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>190500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>136100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>114200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>157500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>119300</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3721,56 +3994,62 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>204600</v>
+      </c>
+      <c r="E60" s="3">
+        <v>225800</v>
+      </c>
+      <c r="F60" s="3">
         <v>315300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>292400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>254600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>348000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>432900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>338200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>254200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>309700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>354100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>325800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>191600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>258200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>260700</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3786,56 +4065,62 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>809700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>773300</v>
+      </c>
+      <c r="F61" s="3">
         <v>805900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>948500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>869100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>779700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>781300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>827900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>784500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>160000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>787700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>789300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>795400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1179600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1182800</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -3851,56 +4136,62 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>182900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>196700</v>
+      </c>
+      <c r="F62" s="3">
         <v>196100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>177300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>178700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>179900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>161500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>149800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>153800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>790000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>121700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>133200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>145300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>135700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>13600</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3916,8 +4207,14 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3981,8 +4278,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4046,8 +4349,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4111,56 +4420,62 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1197200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1195800</v>
+      </c>
+      <c r="F66" s="3">
         <v>1317200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1418200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1302400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1307600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1375800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1315900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1192600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1259800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1263500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1248300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1132300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1573400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1457100</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4176,8 +4491,14 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4201,8 +4522,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4266,8 +4589,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4331,8 +4660,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4396,8 +4731,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4461,56 +4802,62 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-300400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-260800</v>
+      </c>
+      <c r="F72" s="3">
         <v>-277300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-349900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-318300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-288100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-346000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-469000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-461500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-422500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-467000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-585800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-386600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-827200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-869200</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4526,8 +4873,14 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4591,8 +4944,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4656,8 +5015,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4721,56 +5086,62 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-198600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-161400</v>
+      </c>
+      <c r="F76" s="3">
         <v>-179800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-255000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-225600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-198000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-258800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-385700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-381300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-217600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-265700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-391000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-386400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-827000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-869100</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4786,8 +5157,14 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4851,143 +5228,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="F80" s="2">
         <v>45108</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45017</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>44835</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>44744</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44653</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44562</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44471</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44380</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44289</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44198</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44009</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43918</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43827</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43736</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43645</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43554</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43463</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-39600</v>
+      </c>
+      <c r="E81" s="3">
+        <v>16500</v>
+      </c>
+      <c r="F81" s="3">
         <v>72500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-31500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-30300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>57900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>123000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-7400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-14500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>44500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>118800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-6500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-30300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>42100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>71900</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3">
         <v>-26200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>800</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5011,53 +5406,55 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E83" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F83" s="3">
         <v>8100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>8900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>8500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>7900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>7100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>6600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>9200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>7300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>6300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>6300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>6600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>8300</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5067,17 +5464,23 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
-      </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5141,8 +5544,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5206,8 +5615,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5271,8 +5686,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5336,8 +5757,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5401,53 +5828,59 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-71900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>81300</v>
+      </c>
+      <c r="F89" s="3">
         <v>171200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-61600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-184400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-6000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>209400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-11200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-125600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>51200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>229800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>7800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-119300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>17500</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5457,17 +5890,23 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3">
-        <v>0</v>
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5491,53 +5930,55 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="F91" s="3">
         <v>-11900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-9100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-5700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-5800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-11600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-8900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-5400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-11100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-8300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-6800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-2700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-5100</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5547,17 +5988,23 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
-      </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5621,8 +6068,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5686,53 +6139,59 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-11600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-17300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-9800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-13700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-72800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-22300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-33400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-10500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-13200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-9100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-12800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-5100</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
@@ -5742,17 +6201,23 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5776,8 +6241,10 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5841,8 +6308,14 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5906,8 +6379,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5971,8 +6450,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6036,53 +6521,59 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>35500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-33700</v>
+      </c>
+      <c r="F100" s="3">
         <v>-143100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>77400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>88600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-2000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-46000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>43200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-154100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-2000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-2000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-8800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>66600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-4200</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6092,17 +6583,23 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
-      <c r="V100" s="3">
-        <v>0</v>
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6166,53 +6663,59 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>36000</v>
+      </c>
+      <c r="F102" s="3">
         <v>10700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>6000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-109600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-80800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>141200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-1400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-290200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>36000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>218700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-13700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-53000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>8200</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6222,13 +6725,19 @@
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3">
-        <v>0</v>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W102" s="3">
+        <v>0</v>
+      </c>
+      <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LESL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LESL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
   <si>
     <t>LESL</t>
   </si>
@@ -656,168 +656,172 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45290</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44835</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44744</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44653</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44562</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44471</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44380</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44289</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44198</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44107</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44009</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43918</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43827</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43736</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43645</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43554</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43463</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>188700</v>
+      </c>
+      <c r="E8" s="3">
         <v>174000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>432400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>610900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>212800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>195100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>475600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>673600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>228100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>184800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>408900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>596500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>192400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>145000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>381300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>479900</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T8" s="3">
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U8" s="3">
         <v>123000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>298200</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
@@ -827,68 +831,71 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>134300</v>
+      </c>
+      <c r="E9" s="3">
         <v>123600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>272200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>359300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>141700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>129800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>258400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>370000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>142400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>117500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>220900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>312800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>120800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>93300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>214700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>269200</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T9" s="3">
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U9" s="3">
         <v>81900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>166900</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -898,68 +905,71 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>54400</v>
+      </c>
+      <c r="E10" s="3">
         <v>50400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>160200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>251600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>71100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>65300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>217200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>303600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>85700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>67300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>188000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>283700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>71600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>51700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>166600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>210700</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T10" s="3">
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U10" s="3">
         <v>41100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>131300</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -969,8 +979,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -996,8 +1009,9 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1067,8 +1081,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1138,29 +1155,32 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>700</v>
+      </c>
+      <c r="E14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>2300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3500</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
         <v>0</v>
       </c>
@@ -1171,37 +1191,37 @@
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>6400</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>1900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>7300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2300</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1209,8 +1229,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1280,8 +1303,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1304,68 +1330,69 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>219200</v>
+      </c>
+      <c r="E17" s="3">
         <v>210400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>393800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>495100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>238000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>222100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>392500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>501500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>232100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>197300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>341800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>430100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>193000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>178100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>313300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>368300</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T17" s="3">
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U17" s="3">
         <v>141600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>239300</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1375,68 +1402,71 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-30500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-36400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>38600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>115800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-25200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-27000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>83100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>172100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-4000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-12500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>67100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>166400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-33100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>68000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>111600</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U18" s="3">
         <v>-18600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>58900</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1446,8 +1476,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1473,8 +1506,9 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1497,44 +1531,44 @@
         <v>0</v>
       </c>
       <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
         <v>200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-200</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-400</v>
       </c>
       <c r="M20" s="3">
         <v>-400</v>
       </c>
       <c r="N20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O20" s="3">
         <v>-800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1000</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-600</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T20" s="3">
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-3000</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1544,68 +1578,71 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-22700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-28100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>47100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>124000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-16300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-18500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>91000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>179300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-3600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>74000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>171900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>4600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-26500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>76200</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U21" s="3">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3">
         <v>86300</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1615,68 +1652,71 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E22" s="3">
         <v>17100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>17200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>13400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>6800</v>
-      </c>
-      <c r="K22" s="3">
-        <v>6900</v>
       </c>
       <c r="L22" s="3">
         <v>6900</v>
       </c>
       <c r="M22" s="3">
-        <v>7400</v>
+        <v>6900</v>
       </c>
       <c r="N22" s="3">
         <v>7400</v>
       </c>
       <c r="O22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="P22" s="3">
         <v>8100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>18600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>19500</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T22" s="3">
+      <c r="T22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U22" s="3">
         <v>22400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>23900</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1686,68 +1726,71 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-48700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-53500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>21400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>98100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-42400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-40300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>73500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>165400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-11100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-19700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>59300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>158200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-44600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>49300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>91500</v>
       </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T23" s="3">
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U23" s="3">
         <v>-41200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>32000</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1757,68 +1800,71 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-14100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-14000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>25600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-10900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-10100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>15600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>42400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-3700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-5300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>14700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>39400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-14300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>19600</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T24" s="3">
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U24" s="3">
         <v>-15000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>31200</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1828,8 +1874,11 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1899,68 +1948,71 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-39600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>16500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>72500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-31500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-30300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>57900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>123000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-14500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>44500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>118800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-30300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>42100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>71900</v>
       </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T26" s="3">
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U26" s="3">
         <v>-26200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>800</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1970,68 +2022,71 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-39600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>16500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>72500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-31500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-30300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>57900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>123000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-7400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-14500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>44500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>118800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-6500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-30300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>42100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>71900</v>
       </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T27" s="3">
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U27" s="3">
         <v>-26200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>800</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2041,8 +2096,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2112,8 +2170,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2183,8 +2244,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2254,8 +2318,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2325,8 +2392,11 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2349,44 +2419,44 @@
         <v>0</v>
       </c>
       <c r="J32" s="3">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3">
         <v>-200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>200</v>
-      </c>
-      <c r="L32" s="3">
-        <v>400</v>
       </c>
       <c r="M32" s="3">
         <v>400</v>
       </c>
       <c r="N32" s="3">
+        <v>400</v>
+      </c>
+      <c r="O32" s="3">
         <v>800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1000</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>600</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T32" s="3">
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>3000</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2396,68 +2466,71 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-39600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>16500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>72500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-31500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-30300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>57900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>123000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-7400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-14500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>44500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>118800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-6500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-30300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>42100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>71900</v>
       </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T33" s="3">
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U33" s="3">
         <v>-26200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>800</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2467,8 +2540,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2538,68 +2614,71 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-39600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>16500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>72500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-31500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-30300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>57900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>123000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-7400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-14500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>44500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>118800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-6500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-30300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>42100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>71900</v>
       </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T35" s="3">
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U35" s="3">
         <v>-26200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>800</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2609,84 +2688,90 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45290</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44835</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44744</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44653</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44562</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44471</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44380</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44289</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44198</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44107</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44009</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43918</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43827</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43736</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43645</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43554</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43463</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2712,8 +2797,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2739,8 +2825,9 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2748,50 +2835,50 @@
         <v>8400</v>
       </c>
       <c r="E41" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F41" s="3">
         <v>55400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>19400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>112300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>193100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>52000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>53300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>343500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>309100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>88700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>102800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>157100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>148900</v>
       </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2810,8 +2897,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2881,59 +2971,62 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E43" s="3">
         <v>22500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>29400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>49300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>38000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>46400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>45300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>47300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>44200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>39400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>77700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>47800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>94500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>74200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>31500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>35800</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2952,59 +3045,62 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>379100</v>
+      </c>
+      <c r="E44" s="3">
         <v>334000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>311800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>436600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>492300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>429500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>361700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>361400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>345000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>244600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>198800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>224500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>277900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>174500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>149000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>181100</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3023,59 +3119,62 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>33400</v>
+      </c>
+      <c r="E45" s="3">
         <v>27100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>23600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>31500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>52700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>29900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>23100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>30500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>30700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>38200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>41100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>28600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>87300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>65500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>22700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>24600</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3094,59 +3193,62 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>453600</v>
+      </c>
+      <c r="E46" s="3">
         <v>392000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>420300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>536700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>591700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>508500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>542400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>632300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>471900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>375500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>601700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>610100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>448300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>340100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>360200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>390400</v>
       </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3165,8 +3267,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3236,59 +3341,62 @@
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>350000</v>
+      </c>
+      <c r="E48" s="3">
         <v>330700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>341700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>335800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>312000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>308900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>314600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>293300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>279100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>273200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>282600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>235400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>245200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>253800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>244000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>74700</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3307,59 +3415,62 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E49" s="3">
         <v>217900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>218900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>219800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>216600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>218100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>213700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>155700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>146900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>132400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>129000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>127700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>128600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>121200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>122000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>121700</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3378,8 +3489,11 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3449,8 +3563,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3520,59 +3637,62 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>74600</v>
+      </c>
+      <c r="E52" s="3">
         <v>57900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>53500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>45100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>42900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>41300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>39000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>35700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>32400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>30200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>28900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>24600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>35900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>31400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>21000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1200</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3591,8 +3711,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3662,59 +3785,62 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1095200</v>
+      </c>
+      <c r="E54" s="3">
         <v>998500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1034400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1137400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1163200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1076800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1109600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1117000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>930200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>811300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1042200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>997800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>857300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>745800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>746400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>588000</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3733,8 +3859,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3760,8 +3889,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3787,59 +3917,60 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>112400</v>
+      </c>
+      <c r="E57" s="3">
         <v>63500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>58600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>147400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>139800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>117300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>156500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>219000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>160900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>99500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>101000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>155500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>181500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>69000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>92400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>133100</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3858,8 +3989,11 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3900,7 +4034,7 @@
         <v>8100</v>
       </c>
       <c r="P58" s="3">
-        <v>8300</v>
+        <v>8100</v>
       </c>
       <c r="Q58" s="3">
         <v>8300</v>
@@ -3908,8 +4042,8 @@
       <c r="R58" s="3">
         <v>8300</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
+      <c r="S58" s="3">
+        <v>8300</v>
       </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
@@ -3929,59 +4063,62 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>141600</v>
+      </c>
+      <c r="E59" s="3">
         <v>132900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>159200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>159800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>144500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>129200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>183400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>205800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>169200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>146600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>200700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>190500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>136100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>114200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>157500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>119300</v>
       </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4000,59 +4137,62 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>262100</v>
+      </c>
+      <c r="E60" s="3">
         <v>204600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>225800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>315300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>292400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>254600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>348000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>432900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>338200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>254200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>309700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>354100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>325800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>191600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>258200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>260700</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4071,59 +4211,62 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>867200</v>
+      </c>
+      <c r="E61" s="3">
         <v>809700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>773300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>805900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>948500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>869100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>779700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>781300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>827900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>784500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>160000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>787700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>789300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>795400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1179600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1182800</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4142,59 +4285,62 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>197000</v>
+      </c>
+      <c r="E62" s="3">
         <v>182900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>196700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>196100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>177300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>178700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>179900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>161500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>149800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>153800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>790000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>121700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>133200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>145300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>135700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>13600</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4213,8 +4359,11 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4284,8 +4433,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4355,8 +4507,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4426,59 +4581,62 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1326200</v>
+      </c>
+      <c r="E66" s="3">
         <v>1197200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1195800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1317200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1418200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1302400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1307600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1375800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1315900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1192600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1259800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1263500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1248300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1132300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1573400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1457100</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4497,8 +4655,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4524,8 +4685,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4595,8 +4757,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4666,8 +4831,11 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4737,8 +4905,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4808,59 +4979,62 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-334900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-300400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-260800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-277300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-349900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-318300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-288100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-346000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-469000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-461500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-422500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-467000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-585800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-386600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-827200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-869200</v>
       </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
@@ -4879,8 +5053,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4950,8 +5127,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5021,8 +5201,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5092,59 +5275,62 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-231000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-198600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-161400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-179800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-255000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-225600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-198000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-258800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-385700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-381300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-217600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-265700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-391000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-386400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-827000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-869100</v>
       </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5163,8 +5349,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5234,144 +5423,150 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45290</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44835</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44744</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44653</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44562</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44471</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44380</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44289</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44198</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44107</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44009</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43918</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43827</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43736</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43645</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43554</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43463</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-34600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-39600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>16500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>72500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-31500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-30300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>57900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>123000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-7400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-14500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>44500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>118800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-6500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-30300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>42100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>71900</v>
       </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T81" s="3">
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U81" s="3">
         <v>-26200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>800</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5381,8 +5576,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5408,56 +5606,57 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E83" s="3">
         <v>8300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>9200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7300</v>
-      </c>
-      <c r="N83" s="3">
-        <v>6300</v>
       </c>
       <c r="O83" s="3">
         <v>6300</v>
       </c>
       <c r="P83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="Q83" s="3">
         <v>6600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>8300</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5470,8 +5669,8 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -5479,8 +5678,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5550,8 +5752,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5621,8 +5826,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5692,8 +5900,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5763,8 +5974,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5834,56 +6048,59 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-43200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-71900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>81300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>171200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-61600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-184400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-6000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>209400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-11200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-125600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>51200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>229800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-119300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>17500</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S89" s="3" t="s">
         <v>3</v>
       </c>
@@ -5896,8 +6113,8 @@
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W89" s="3">
-        <v>0</v>
+      <c r="W89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X89" s="3">
         <v>0</v>
@@ -5905,8 +6122,11 @@
       <c r="Y89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5932,56 +6152,57 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-5700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5100</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5994,8 +6215,8 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -6003,8 +6224,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6074,8 +6298,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6145,56 +6372,59 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-17300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-72800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-22300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-33400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-10500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-12800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5100</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6207,8 +6437,8 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
@@ -6216,8 +6446,11 @@
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6243,8 +6476,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6314,8 +6548,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6385,8 +6622,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6456,8 +6696,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6527,56 +6770,59 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>56500</v>
+      </c>
+      <c r="E100" s="3">
         <v>35500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-33700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-143100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>77400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>88600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-46000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>43200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-154100</v>
-      </c>
-      <c r="M100" s="3">
-        <v>-2000</v>
       </c>
       <c r="N100" s="3">
         <v>-2000</v>
       </c>
       <c r="O100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="P100" s="3">
         <v>-8800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>66600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-4200</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6589,8 +6835,8 @@
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
+      <c r="W100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X100" s="3">
         <v>0</v>
@@ -6598,8 +6844,11 @@
       <c r="Y100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6669,56 +6918,59 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-47000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>36000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-109600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-80800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>141200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-290200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>36000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>218700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-53000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>8200</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6731,13 +6983,16 @@
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
+      <c r="W102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X102" s="3">
         <v>0</v>
       </c>
       <c r="Y102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LESL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LESL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
   <si>
     <t>LESL</t>
   </si>
@@ -656,175 +656,179 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45290</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44744</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44653</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44562</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44471</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44380</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44289</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44198</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44107</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44009</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43918</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43827</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43736</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43645</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43554</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43463</v>
       </c>
-      <c r="Z7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>569600</v>
+      </c>
+      <c r="E8" s="3">
         <v>188700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>174000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>432400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>610900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>212800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>195100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>475600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>673600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>228100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>184800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>408900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>596500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>192400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>145000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>381300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>479900</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U8" s="3">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3">
         <v>123000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>298200</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
@@ -834,71 +838,74 @@
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>340800</v>
+      </c>
+      <c r="E9" s="3">
         <v>134300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>123600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>272200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>359300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>141700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>129800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>258400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>370000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>142400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>117500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>220900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>312800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>120800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>93300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>214700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>269200</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U9" s="3">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3">
         <v>81900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>166900</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
@@ -908,71 +915,74 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>228800</v>
+      </c>
+      <c r="E10" s="3">
         <v>54400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>50400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>160200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>251600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>71100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>65300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>217200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>303600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>85700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>67300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>188000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>283700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>71600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>51700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>166600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>210700</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U10" s="3">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3">
         <v>41100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>131300</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
@@ -982,8 +992,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1010,8 +1023,9 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1084,8 +1098,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1158,32 +1175,35 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E14" s="3">
         <v>700</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>2300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3500</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
@@ -1194,37 +1214,37 @@
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>6400</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>1900</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>7300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2300</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1232,8 +1252,11 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1306,8 +1329,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1331,71 +1357,72 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>471900</v>
+      </c>
+      <c r="E17" s="3">
         <v>219200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>210400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>393800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>495100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>238000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>222100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>392500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>501500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>232100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>197300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>341800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>430100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>193000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>178100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>313300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>368300</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U17" s="3">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3">
         <v>141600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>239300</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1405,71 +1432,74 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>97700</v>
+      </c>
+      <c r="E18" s="3">
         <v>-30500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-36400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>38600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>115800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-25200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-27000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>83100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>172100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-4000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-12500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>67100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>166400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-33100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>68000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>111600</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U18" s="3">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3">
         <v>-18600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>58900</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1479,8 +1509,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1507,8 +1540,9 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1534,44 +1568,44 @@
         <v>0</v>
       </c>
       <c r="K20" s="3">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3">
         <v>200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-200</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-400</v>
       </c>
       <c r="N20" s="3">
         <v>-400</v>
       </c>
       <c r="O20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P20" s="3">
         <v>-800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-600</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U20" s="3">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3">
         <v>-200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-3000</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1581,71 +1615,74 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>105900</v>
+      </c>
+      <c r="E21" s="3">
         <v>-22700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-28100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>47100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>124000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-16300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-18500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>91000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>179300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-3600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>74000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>171900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-26500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>76200</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V21" s="3">
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W21" s="3">
         <v>86300</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1655,8 +1692,11 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1664,62 +1704,62 @@
         <v>18200</v>
       </c>
       <c r="E22" s="3">
+        <v>18200</v>
+      </c>
+      <c r="F22" s="3">
         <v>17100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>17700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>17200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>13400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>6800</v>
-      </c>
-      <c r="L22" s="3">
-        <v>6900</v>
       </c>
       <c r="M22" s="3">
         <v>6900</v>
       </c>
       <c r="N22" s="3">
-        <v>7400</v>
+        <v>6900</v>
       </c>
       <c r="O22" s="3">
         <v>7400</v>
       </c>
       <c r="P22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="Q22" s="3">
         <v>8100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>11500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>18600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>19500</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U22" s="3">
+      <c r="U22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V22" s="3">
         <v>22400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>23900</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1729,71 +1769,74 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>79500</v>
+      </c>
+      <c r="E23" s="3">
         <v>-48700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-53500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>21400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>98100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-42400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-40300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>73500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>165400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-11100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-19700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>59300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>158200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-44600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>49300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>91500</v>
       </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U23" s="3">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3">
         <v>-41200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>32000</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1803,71 +1846,74 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>18900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-14100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-14000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>25600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-10900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-10100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>42400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-3700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-5300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>14700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>39400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-14300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>7200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>19600</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U24" s="3">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3">
         <v>-15000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>31200</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1877,8 +1923,11 @@
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1951,71 +2000,74 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-34600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-39600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>16500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>72500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-31500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-30300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>57900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>123000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-7400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-14500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>44500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>118800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-30300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>42100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>71900</v>
       </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U26" s="3">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3">
         <v>-26200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>800</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2025,71 +2077,74 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-34600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-39600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>72500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-31500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-30300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>57900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>123000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-7400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-14500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>44500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>118800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-30300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>42100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>71900</v>
       </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U27" s="3">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3">
         <v>-26200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>800</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2099,8 +2154,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2173,8 +2231,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2247,8 +2308,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2321,8 +2385,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2395,8 +2462,11 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2422,44 +2492,44 @@
         <v>0</v>
       </c>
       <c r="K32" s="3">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3">
         <v>-200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>200</v>
-      </c>
-      <c r="M32" s="3">
-        <v>400</v>
       </c>
       <c r="N32" s="3">
         <v>400</v>
       </c>
       <c r="O32" s="3">
+        <v>400</v>
+      </c>
+      <c r="P32" s="3">
         <v>800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1000</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>600</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U32" s="3">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3">
         <v>200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>3000</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2469,71 +2539,74 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-34600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-39600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>16500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>72500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-31500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-30300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>57900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>123000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-7400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-14500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>44500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>118800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-30300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>42100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>71900</v>
       </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U33" s="3">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3">
         <v>-26200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>800</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2543,8 +2616,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2617,71 +2693,74 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-34600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-39600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>16500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>72500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-31500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-30300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>57900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>123000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-7400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-14500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>44500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>118800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-30300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>42100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>71900</v>
       </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U35" s="3">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3">
         <v>-26200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>800</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2691,87 +2770,93 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45290</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44744</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44653</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44562</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44471</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44380</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44289</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44198</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44107</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44009</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43918</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43827</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43736</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43645</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43554</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43463</v>
       </c>
-      <c r="Z38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2798,8 +2883,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2826,62 +2912,63 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>8400</v>
+        <v>74400</v>
       </c>
       <c r="E41" s="3">
         <v>8400</v>
       </c>
       <c r="F41" s="3">
+        <v>8400</v>
+      </c>
+      <c r="G41" s="3">
         <v>55400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>19400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>112300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>193100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>52000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>53300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>343500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>309100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>88700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>102800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>157100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>148900</v>
       </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2900,8 +2987,11 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2974,62 +3064,65 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>48200</v>
+      </c>
+      <c r="E43" s="3">
         <v>32700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>22500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>29400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>49300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>38000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>46400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>45300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>47300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>44200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>39400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>77700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>47800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>94500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>74200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>31500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>35800</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3048,62 +3141,65 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>302200</v>
+      </c>
+      <c r="E44" s="3">
         <v>379100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>334000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>311800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>436600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>492300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>429500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>361700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>361400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>345000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>244600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>198800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>224500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>277900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>174500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>149000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>181100</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3122,62 +3218,65 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>32200</v>
+      </c>
+      <c r="E45" s="3">
         <v>33400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>27100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>23600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>31500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>52700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>29900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>23100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>30500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>30700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>41100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>28600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>87300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>65500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>22700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>24600</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3196,62 +3295,65 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>457000</v>
+      </c>
+      <c r="E46" s="3">
         <v>453600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>392000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>420300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>536700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>591700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>508500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>542400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>632300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>471900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>375500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>601700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>610100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>448300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>340100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>360200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>390400</v>
       </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3270,8 +3372,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3344,62 +3449,65 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>376700</v>
+      </c>
+      <c r="E48" s="3">
         <v>350000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>330700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>341700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>335800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>312000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>308900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>314600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>293300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>279100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>273200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>282600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>235400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>245200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>253800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>244000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>74700</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3418,62 +3526,65 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>216000</v>
+      </c>
+      <c r="E49" s="3">
         <v>217000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>217900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>218900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>219800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>216600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>218100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>213700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>155700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>146900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>132400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>129000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>127700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>128600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>121200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>122000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>121700</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3492,8 +3603,11 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3566,8 +3680,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3640,62 +3757,65 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>55400</v>
+      </c>
+      <c r="E52" s="3">
         <v>74600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>57900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>53500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>45100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>42900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>41300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>39000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>35700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>32400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>30200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>28900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>24600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>35900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>31400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>21000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1200</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3714,8 +3834,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3788,62 +3911,65 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1105200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1095200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>998500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1034400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1137400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1163200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1076800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1109600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1117000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>930200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>811300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1042200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>997800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>857300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>745800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>746400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>588000</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3862,8 +3988,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3890,8 +4019,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3918,62 +4048,63 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>108900</v>
+      </c>
+      <c r="E57" s="3">
         <v>112400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>63500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>58600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>147400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>139800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>117300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>156500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>219000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>160900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>99500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>101000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>155500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>181500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>69000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>92400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>133100</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
       </c>
@@ -3992,8 +4123,11 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4037,7 +4171,7 @@
         <v>8100</v>
       </c>
       <c r="Q58" s="3">
-        <v>8300</v>
+        <v>8100</v>
       </c>
       <c r="R58" s="3">
         <v>8300</v>
@@ -4045,8 +4179,8 @@
       <c r="S58" s="3">
         <v>8300</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
+      <c r="T58" s="3">
+        <v>8300</v>
       </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
@@ -4066,62 +4200,65 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>168800</v>
+      </c>
+      <c r="E59" s="3">
         <v>141600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>132900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>159200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>159800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>144500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>129200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>183400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>205800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>169200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>146600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>200700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>190500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>136100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>114200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>157500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>119300</v>
       </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4140,62 +4277,65 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>285900</v>
+      </c>
+      <c r="E60" s="3">
         <v>262100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>204600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>225800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>315300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>292400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>254600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>348000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>432900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>338200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>254200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>309700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>354100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>325800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>191600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>258200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>260700</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4214,62 +4354,65 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>768600</v>
+      </c>
+      <c r="E61" s="3">
         <v>867200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>809700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>773300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>805900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>948500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>869100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>779700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>781300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>827900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>784500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>160000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>787700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>789300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>795400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1179600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1182800</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4288,62 +4431,65 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>218900</v>
+      </c>
+      <c r="E62" s="3">
         <v>197000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>182900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>196700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>196100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>177300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>178700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>179900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>161500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>149800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>153800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>790000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>121700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>133200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>145300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>135700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>13600</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4362,8 +4508,11 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4436,8 +4585,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4510,8 +4662,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4584,62 +4739,65 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1273300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1326200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1197200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1195800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1317200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1418200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1302400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1307600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1375800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1315900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1192600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1259800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1263500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1248300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1132300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1573400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1457100</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4658,8 +4816,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4686,8 +4847,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4760,8 +4922,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4834,8 +4999,11 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4908,8 +5076,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4982,62 +5153,65 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-274300</v>
+      </c>
+      <c r="E72" s="3">
         <v>-334900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-300400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-260800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-277300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-349900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-318300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-288100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-346000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-469000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-461500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-422500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-467000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-585800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-386600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-827200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-869200</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5056,8 +5230,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5130,8 +5307,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5204,8 +5384,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5278,62 +5461,65 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-168200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-231000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-198600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-161400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-179800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-255000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-225600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-198000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-258800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-385700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-381300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-217600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-265700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-391000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-386400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-827000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-869100</v>
       </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5352,8 +5538,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5426,150 +5615,156 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45290</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44744</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44653</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44562</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44471</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44380</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44289</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44198</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44107</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44009</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43918</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43827</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43736</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43645</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43554</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43463</v>
       </c>
-      <c r="Z80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-34600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-39600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>16500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>72500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-31500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-30300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>57900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>123000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-7400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-14500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>44500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>118800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-30300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>42100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>71900</v>
       </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="U81" s="3">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3">
         <v>-26200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>800</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5579,8 +5774,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5607,59 +5805,60 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E83" s="3">
         <v>7800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>8600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>8500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>9200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>6300</v>
       </c>
       <c r="P83" s="3">
         <v>6300</v>
       </c>
       <c r="Q83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="R83" s="3">
         <v>6600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>8300</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5672,8 +5871,8 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -5681,8 +5880,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5755,8 +5957,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5829,8 +6034,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5903,8 +6111,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5977,8 +6188,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6051,59 +6265,62 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>175500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-43200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-71900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>81300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>171200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-61600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-184400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-6000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>209400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-11200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-125600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>51200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>229800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-119300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>17500</v>
       </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6116,8 +6333,8 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X89" s="3">
-        <v>0</v>
+      <c r="X89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y89" s="3">
         <v>0</v>
@@ -6125,8 +6342,11 @@
       <c r="Z89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6153,59 +6373,60 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-5700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5100</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6218,8 +6439,8 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -6227,8 +6448,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6301,8 +6525,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6375,59 +6602,62 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-13700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-72800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-22300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-33400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5100</v>
       </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6440,8 +6670,8 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
@@ -6449,8 +6679,11 @@
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6477,8 +6710,9 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6551,8 +6785,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6625,8 +6862,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6699,8 +6939,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6773,59 +7016,62 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-99200</v>
+      </c>
+      <c r="E100" s="3">
         <v>56500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>35500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-33700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-143100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>77400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>88600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-46000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>43200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-154100</v>
-      </c>
-      <c r="N100" s="3">
-        <v>-2000</v>
       </c>
       <c r="O100" s="3">
         <v>-2000</v>
       </c>
       <c r="P100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="Q100" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>66600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4200</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6838,8 +7084,8 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
+      <c r="X100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y100" s="3">
         <v>0</v>
@@ -6847,8 +7093,11 @@
       <c r="Z100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6921,59 +7170,62 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>66000</v>
       </c>
       <c r="E102" s="3">
+        <v>0</v>
+      </c>
+      <c r="F102" s="3">
         <v>-47000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>36000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-109600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-80800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>141200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-290200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>36000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>218700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-53000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>8200</v>
       </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
@@ -6986,13 +7238,16 @@
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
+      <c r="X102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y102" s="3">
         <v>0</v>
       </c>
       <c r="Z102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LESL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LESL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="92">
   <si>
     <t>LESL</t>
   </si>
@@ -656,182 +656,186 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45290</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44835</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44744</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44653</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44562</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44471</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44380</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44289</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44198</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44107</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44009</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43918</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43827</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43736</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43645</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43554</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43463</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>397900</v>
+      </c>
+      <c r="E8" s="3">
         <v>569600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>188700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>174000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>432400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>610900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>212800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>195100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>475600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>673600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>228100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>184800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>408900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>596500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>192400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>145000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>381300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>479900</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V8" s="3">
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W8" s="3">
         <v>123000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>298200</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
@@ -841,74 +845,77 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>254600</v>
+      </c>
+      <c r="E9" s="3">
         <v>340800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>134300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>123600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>272200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>359300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>141700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>129800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>258400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>370000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>142400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>117500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>220900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>312800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>120800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>93300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>214700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>269200</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W9" s="3">
         <v>81900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>166900</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
@@ -918,74 +925,77 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>143200</v>
+      </c>
+      <c r="E10" s="3">
         <v>228800</v>
       </c>
-      <c r="E10" s="3">
-        <v>54400</v>
-      </c>
       <c r="F10" s="3">
+        <v>54300</v>
+      </c>
+      <c r="G10" s="3">
         <v>50400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>160200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>251600</v>
       </c>
-      <c r="I10" s="3">
-        <v>71100</v>
-      </c>
       <c r="J10" s="3">
+        <v>71200</v>
+      </c>
+      <c r="K10" s="3">
         <v>65300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>217200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>303600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>85700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>67300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>188000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>283700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>71600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>51700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>166600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>210700</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W10" s="3">
         <v>41100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>131300</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
@@ -995,8 +1005,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1024,8 +1037,9 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1101,8 +1115,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1178,35 +1195,38 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E14" s="3">
         <v>1300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>9700</v>
+      </c>
+      <c r="I14" s="3">
         <v>2300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3500</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1217,37 +1237,37 @@
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>6400</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>1900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>7300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>2300</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1255,31 +1275,34 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>8700</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>8200</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>8600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>8100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>8900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1332,8 +1355,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1358,74 +1384,75 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>471900</v>
+        <v>364500</v>
       </c>
       <c r="E17" s="3">
-        <v>219200</v>
+        <v>470700</v>
       </c>
       <c r="F17" s="3">
-        <v>210400</v>
+        <v>218500</v>
       </c>
       <c r="G17" s="3">
-        <v>393800</v>
+        <v>209400</v>
       </c>
       <c r="H17" s="3">
-        <v>495100</v>
+        <v>384100</v>
       </c>
       <c r="I17" s="3">
-        <v>238000</v>
+        <v>492800</v>
       </c>
       <c r="J17" s="3">
+        <v>233900</v>
+      </c>
+      <c r="K17" s="3">
         <v>222100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>392500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>501500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>232100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>197300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>341800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>430100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>193000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>178100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>313300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>368300</v>
       </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V17" s="3">
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W17" s="3">
         <v>141600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>239300</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1435,74 +1462,77 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>97700</v>
+        <v>33300</v>
       </c>
       <c r="E18" s="3">
-        <v>-30500</v>
+        <v>99000</v>
       </c>
       <c r="F18" s="3">
-        <v>-36400</v>
+        <v>-29800</v>
       </c>
       <c r="G18" s="3">
-        <v>38600</v>
+        <v>-35500</v>
       </c>
       <c r="H18" s="3">
-        <v>115800</v>
+        <v>48300</v>
       </c>
       <c r="I18" s="3">
-        <v>-25200</v>
+        <v>118100</v>
       </c>
       <c r="J18" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="K18" s="3">
         <v>-27000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>83100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>172100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-4000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-12500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>67100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>166400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-33100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>68000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>111600</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V18" s="3">
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W18" s="3">
         <v>-18600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>58900</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1512,8 +1542,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1541,74 +1574,75 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
       <c r="L20" s="3">
+        <v>0</v>
+      </c>
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-200</v>
-      </c>
-      <c r="N20" s="3">
-        <v>-400</v>
       </c>
       <c r="O20" s="3">
         <v>-400</v>
       </c>
       <c r="P20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1000</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-600</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V20" s="3">
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3000</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1618,74 +1652,77 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>105900</v>
+        <v>42000</v>
       </c>
       <c r="E21" s="3">
-        <v>-22700</v>
+        <v>107200</v>
       </c>
       <c r="F21" s="3">
-        <v>-28100</v>
+        <v>-22000</v>
       </c>
       <c r="G21" s="3">
-        <v>47100</v>
+        <v>-27100</v>
       </c>
       <c r="H21" s="3">
-        <v>124000</v>
+        <v>56900</v>
       </c>
       <c r="I21" s="3">
-        <v>-16300</v>
+        <v>126300</v>
       </c>
       <c r="J21" s="3">
+        <v>-12100</v>
+      </c>
+      <c r="K21" s="3">
         <v>-18500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>91000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>179300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-3600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>74000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>171900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-26500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>76200</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W21" s="3">
+      <c r="W21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X21" s="3">
         <v>86300</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1695,74 +1732,77 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>18200</v>
+        <v>17000</v>
       </c>
       <c r="E22" s="3">
         <v>18200</v>
       </c>
       <c r="F22" s="3">
+        <v>18200</v>
+      </c>
+      <c r="G22" s="3">
         <v>17100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>17200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>17700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>17200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>6800</v>
-      </c>
-      <c r="M22" s="3">
-        <v>6900</v>
       </c>
       <c r="N22" s="3">
         <v>6900</v>
       </c>
       <c r="O22" s="3">
-        <v>7400</v>
+        <v>6900</v>
       </c>
       <c r="P22" s="3">
         <v>7400</v>
       </c>
       <c r="Q22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="R22" s="3">
         <v>8100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>11500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>18600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19500</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V22" s="3">
+      <c r="V22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W22" s="3">
         <v>22400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>23900</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1772,74 +1812,77 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E23" s="3">
         <v>79500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-48700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-53500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>21400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>98100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-42400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-40300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>73500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>165400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-11100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-19700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>59300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>158200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-44600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>49300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>91500</v>
       </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V23" s="3">
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W23" s="3">
         <v>-41200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>32000</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1849,74 +1892,77 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E24" s="3">
         <v>18900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-14100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-14000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>25600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-10900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-10100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>42400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-3700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-5300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>14700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>39400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-3300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-14300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>7200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>19600</v>
       </c>
-      <c r="U24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V24" s="3">
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W24" s="3">
         <v>-15000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>31200</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1926,8 +1972,11 @@
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2003,74 +2052,77 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E26" s="3">
         <v>60700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-34600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-39600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>16500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>72500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-31500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-30300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>57900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>123000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-7400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-14500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>44500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>118800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-30300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>42100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>71900</v>
       </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V26" s="3">
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W26" s="3">
         <v>-26200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>800</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2080,74 +2132,77 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E27" s="3">
         <v>60700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-34600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-39600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>16500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>72500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-31500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-30300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>57900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>123000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-7400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-14500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>44500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>118800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-6500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-30300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>42100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>71900</v>
       </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V27" s="3">
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W27" s="3">
         <v>-26200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>800</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2157,8 +2212,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2234,8 +2292,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2311,8 +2372,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2388,8 +2452,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2465,74 +2532,77 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
       <c r="L32" s="3">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>200</v>
-      </c>
-      <c r="N32" s="3">
-        <v>400</v>
       </c>
       <c r="O32" s="3">
         <v>400</v>
       </c>
       <c r="P32" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q32" s="3">
         <v>800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1000</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>600</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V32" s="3">
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3000</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2542,74 +2612,77 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E33" s="3">
         <v>60700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-34600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-39600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>16500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>72500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-31500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-30300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>57900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>123000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-7400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-14500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>44500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>118800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-6500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-30300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>42100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>71900</v>
       </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V33" s="3">
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W33" s="3">
         <v>-26200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>800</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2619,8 +2692,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2696,74 +2772,77 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E35" s="3">
         <v>60700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-34600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-39600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>16500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>72500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-31500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-30300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>57900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>123000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-7400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-14500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>44500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>118800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-6500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-30300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>42100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>71900</v>
       </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V35" s="3">
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W35" s="3">
         <v>-26200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>800</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2773,90 +2852,96 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45290</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44835</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44744</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44653</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44562</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44471</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44380</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44289</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44198</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44107</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44009</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43918</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43827</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43736</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43645</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43554</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43463</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2884,8 +2969,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2913,65 +2999,66 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>108500</v>
+      </c>
+      <c r="E41" s="3">
         <v>74400</v>
-      </c>
-      <c r="E41" s="3">
-        <v>8400</v>
       </c>
       <c r="F41" s="3">
         <v>8400</v>
       </c>
       <c r="G41" s="3">
+        <v>8400</v>
+      </c>
+      <c r="H41" s="3">
         <v>55400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>19400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>112300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>193100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>52000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>53300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>343500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>309100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>88700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>102800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>157100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>148900</v>
       </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
       </c>
@@ -2990,8 +3077,11 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3067,65 +3157,68 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E43" s="3">
         <v>48200</v>
       </c>
-      <c r="E43" s="3">
-        <v>32700</v>
-      </c>
       <c r="F43" s="3">
+        <v>34400</v>
+      </c>
+      <c r="G43" s="3">
         <v>22500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>29400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>49300</v>
       </c>
-      <c r="I43" s="3">
-        <v>38000</v>
-      </c>
       <c r="J43" s="3">
+        <v>60400</v>
+      </c>
+      <c r="K43" s="3">
         <v>46400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>45300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>47300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>44200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>39400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>77700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>47800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>94500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>74200</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>31500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>35800</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3144,65 +3237,68 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>234300</v>
+      </c>
+      <c r="E44" s="3">
         <v>302200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>379100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>334000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>311800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>436600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>492300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>429500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>361700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>361400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>345000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>244600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>198800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>224500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>277900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>174500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>149000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>181100</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3221,65 +3317,68 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>32200</v>
+        <v>9400</v>
       </c>
       <c r="E45" s="3">
-        <v>33400</v>
+        <v>9100</v>
       </c>
       <c r="F45" s="3">
-        <v>27100</v>
+        <v>13000</v>
       </c>
       <c r="G45" s="3">
-        <v>23600</v>
+        <v>12000</v>
       </c>
       <c r="H45" s="3">
-        <v>31500</v>
+        <v>5900</v>
       </c>
       <c r="I45" s="3">
-        <v>52700</v>
+        <v>13900</v>
       </c>
       <c r="J45" s="3">
+        <v>15300</v>
+      </c>
+      <c r="K45" s="3">
         <v>29900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>23100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>30500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>30700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>38200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>41100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>28600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>87300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>65500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>22700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>24600</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3298,65 +3397,68 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>422400</v>
+      </c>
+      <c r="E46" s="3">
         <v>457000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>453600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>392000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>420300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>536700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>591700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>508500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>542400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>632300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>471900</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>375500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>601700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>610100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>448300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>340100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>360200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>390400</v>
       </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3375,31 +3477,34 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -3452,65 +3557,68 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>368900</v>
+      </c>
+      <c r="E48" s="3">
         <v>376700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>350000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>330700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>341700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>335800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>312000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>308900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>314600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>293300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>279100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>273200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>282600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>235400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>245200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>253800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>244000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>74700</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3529,65 +3637,68 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>215100</v>
+      </c>
+      <c r="E49" s="3">
         <v>216000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>217000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>217900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>218900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>219800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>216600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>218100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>213700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>155700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>146900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>132400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>129000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>127700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>128600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>121200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>122000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>121700</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3606,8 +3717,11 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3683,8 +3797,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3760,65 +3877,68 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>55400</v>
+        <v>39700</v>
       </c>
       <c r="E52" s="3">
-        <v>74600</v>
+        <v>40000</v>
       </c>
       <c r="F52" s="3">
-        <v>57900</v>
+        <v>40300</v>
       </c>
       <c r="G52" s="3">
-        <v>53500</v>
+        <v>41900</v>
       </c>
       <c r="H52" s="3">
-        <v>45100</v>
+        <v>46000</v>
       </c>
       <c r="I52" s="3">
+        <v>44900</v>
+      </c>
+      <c r="J52" s="3">
         <v>42900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>41300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>39000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>35700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>32400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>30200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>28900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>24600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>35900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>31400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>21000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1200</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3837,8 +3957,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3914,65 +4037,68 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1050300</v>
+      </c>
+      <c r="E54" s="3">
         <v>1105200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1095200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>998500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1034400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1137400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1163200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1076800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1109600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1117000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>930200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>811300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1042200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>997800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>857300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>745800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>746400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>588000</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3991,8 +4117,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4020,8 +4149,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4049,65 +4179,66 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>67600</v>
+      </c>
+      <c r="E57" s="3">
         <v>108900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>112400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>63500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>58600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>147400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>139800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>117300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>156500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>219000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>160900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>99500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>101000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>155500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>181500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>69000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>92400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>133100</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4126,31 +4257,34 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>8100</v>
+        <v>71800</v>
       </c>
       <c r="E58" s="3">
-        <v>8100</v>
+        <v>69700</v>
       </c>
       <c r="F58" s="3">
-        <v>8100</v>
+        <v>69700</v>
       </c>
       <c r="G58" s="3">
-        <v>8100</v>
+        <v>71200</v>
       </c>
       <c r="H58" s="3">
-        <v>8100</v>
+        <v>70900</v>
       </c>
       <c r="I58" s="3">
-        <v>8100</v>
+        <v>69400</v>
       </c>
       <c r="J58" s="3">
-        <v>8100</v>
+        <v>69700</v>
       </c>
       <c r="K58" s="3">
         <v>8100</v>
@@ -4174,7 +4308,7 @@
         <v>8100</v>
       </c>
       <c r="R58" s="3">
-        <v>8300</v>
+        <v>8100</v>
       </c>
       <c r="S58" s="3">
         <v>8300</v>
@@ -4182,8 +4316,8 @@
       <c r="T58" s="3">
         <v>8300</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
+      <c r="U58" s="3">
+        <v>8300</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
@@ -4203,65 +4337,68 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>168800</v>
+        <v>12700</v>
       </c>
       <c r="E59" s="3">
-        <v>141600</v>
+        <v>12100</v>
       </c>
       <c r="F59" s="3">
-        <v>132900</v>
+        <v>13900</v>
       </c>
       <c r="G59" s="3">
-        <v>159200</v>
+        <v>11800</v>
       </c>
       <c r="H59" s="3">
-        <v>159800</v>
+        <v>19900</v>
       </c>
       <c r="I59" s="3">
-        <v>144500</v>
+        <v>16800</v>
       </c>
       <c r="J59" s="3">
+        <v>15100</v>
+      </c>
+      <c r="K59" s="3">
         <v>129200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>183400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>205800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>169200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>146600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>200700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>190500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>136100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>114200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>157500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>119300</v>
       </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4280,65 +4417,68 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>246900</v>
+      </c>
+      <c r="E60" s="3">
         <v>285900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>262100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>204600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>225800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>315300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>292400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>254600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>348000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>432900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>338200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>254200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>309700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>354100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>325800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>191600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>258200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>260700</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4357,65 +4497,68 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>768600</v>
+        <v>978300</v>
       </c>
       <c r="E61" s="3">
-        <v>867200</v>
+        <v>985400</v>
       </c>
       <c r="F61" s="3">
-        <v>809700</v>
+        <v>1061000</v>
       </c>
       <c r="G61" s="3">
-        <v>773300</v>
+        <v>989100</v>
       </c>
       <c r="H61" s="3">
-        <v>805900</v>
+        <v>966500</v>
       </c>
       <c r="I61" s="3">
-        <v>948500</v>
+        <v>998900</v>
       </c>
       <c r="J61" s="3">
+        <v>1122100</v>
+      </c>
+      <c r="K61" s="3">
         <v>869100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>779700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>781300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>827900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>784500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>160000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>787700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>789300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>795400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1179600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1182800</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4434,65 +4577,68 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>218900</v>
+        <v>2300</v>
       </c>
       <c r="E62" s="3">
-        <v>197000</v>
+        <v>2100</v>
       </c>
       <c r="F62" s="3">
-        <v>182900</v>
+        <v>3100</v>
       </c>
       <c r="G62" s="3">
-        <v>196700</v>
+        <v>3500</v>
       </c>
       <c r="H62" s="3">
-        <v>196100</v>
+        <v>3500</v>
       </c>
       <c r="I62" s="3">
-        <v>177300</v>
+        <v>3100</v>
       </c>
       <c r="J62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="K62" s="3">
         <v>178700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>179900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>161500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>149800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>153800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>790000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>121700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>133200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>145300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>135700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>13600</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4511,8 +4657,11 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4588,8 +4737,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4665,8 +4817,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4742,65 +4897,68 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1227500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1273300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1326200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1197200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1195800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1317200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1418200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1302400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1307600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1375800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1315900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1192600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1259800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1263500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1248300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1132300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1573400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1457100</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4819,8 +4977,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4848,8 +5009,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4925,8 +5087,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5002,8 +5167,11 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5079,8 +5247,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5156,65 +5327,68 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-284200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-274300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-334900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-300400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-260800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-277300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-349900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-318300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-288100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-346000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-469000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-461500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-422500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-467000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-585800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-386600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-827200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-869200</v>
       </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5233,8 +5407,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5310,8 +5487,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5387,8 +5567,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5464,65 +5647,68 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-177100</v>
+      </c>
+      <c r="E76" s="3">
         <v>-168200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-231000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-198600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-161400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-179800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-255000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-225600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-198000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-258800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-385700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-381300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-217600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-265700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-391000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-386400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-827000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-869100</v>
       </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5541,8 +5727,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5618,156 +5807,162 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45290</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44835</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44744</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44653</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44562</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44471</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44380</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44289</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44198</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44107</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44009</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43918</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43827</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43736</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43645</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43554</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43463</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-9900</v>
+      </c>
+      <c r="E81" s="3">
         <v>60700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-34600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-39600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>16500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>72500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-31500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-30300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>57900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>123000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-7400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-14500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>44500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>118800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-6500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-30300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>42100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>71900</v>
       </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="V81" s="3">
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="W81" s="3">
         <v>-26200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>800</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5777,8 +5972,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5806,62 +6004,63 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>8200</v>
+        <v>7700</v>
       </c>
       <c r="E83" s="3">
-        <v>7800</v>
+        <v>6900</v>
       </c>
       <c r="F83" s="3">
-        <v>8300</v>
+        <v>7600</v>
       </c>
       <c r="G83" s="3">
-        <v>8600</v>
+        <v>7600</v>
       </c>
       <c r="H83" s="3">
-        <v>8100</v>
+        <v>7000</v>
       </c>
       <c r="I83" s="3">
-        <v>8900</v>
+        <v>6400</v>
       </c>
       <c r="J83" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K83" s="3">
         <v>8500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>9200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7300</v>
-      </c>
-      <c r="P83" s="3">
-        <v>6300</v>
       </c>
       <c r="Q83" s="3">
         <v>6300</v>
       </c>
       <c r="R83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="S83" s="3">
         <v>6600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>8300</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5874,8 +6073,8 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -5883,8 +6082,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5960,8 +6162,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6037,8 +6242,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6114,8 +6322,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6191,8 +6402,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6268,62 +6482,65 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>47100</v>
+      </c>
+      <c r="E89" s="3">
         <v>175500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-43200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-71900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>81300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>171200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-61600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-184400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-6000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>209400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-11200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-125600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>51200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>229800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>7800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-119300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>17500</v>
       </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6336,8 +6553,8 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y89" s="3">
-        <v>0</v>
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z89" s="3">
         <v>0</v>
@@ -6345,8 +6562,11 @@
       <c r="AA89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6374,62 +6594,63 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5100</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6442,8 +6663,8 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -6451,8 +6672,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6528,8 +6752,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6605,62 +6832,65 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-17300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-13700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-72800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-22300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-33400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-13200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-9100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5100</v>
       </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6673,8 +6903,8 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
@@ -6682,8 +6912,11 @@
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6711,31 +6944,32 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6788,8 +7022,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6865,8 +7102,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6942,8 +7182,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7019,62 +7262,65 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-99200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>56500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>35500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-33700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-143100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>77400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>88600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-46000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>43200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-154100</v>
-      </c>
-      <c r="O100" s="3">
-        <v>-2000</v>
       </c>
       <c r="P100" s="3">
         <v>-2000</v>
       </c>
       <c r="Q100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="R100" s="3">
         <v>-8800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>66600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-4200</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7087,8 +7333,8 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z100" s="3">
         <v>0</v>
@@ -7096,31 +7342,34 @@
       <c r="AA100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -7173,62 +7422,65 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E102" s="3">
         <v>66000</v>
       </c>
-      <c r="E102" s="3">
-        <v>0</v>
-      </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
         <v>-47000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>36000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>6000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-109600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-80800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>141200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-290200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>36000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>218700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-13700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-53000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>8200</v>
       </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7241,13 +7493,16 @@
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y102" s="3">
-        <v>0</v>
+      <c r="Y102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z102" s="3">
         <v>0</v>
       </c>
       <c r="AA102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LESL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LESL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
   <si>
     <t>LESL</t>
   </si>
@@ -656,189 +656,192 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E7" s="2">
         <v>45563</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45472</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45381</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45290</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45108</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45017</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44835</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44744</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44653</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44562</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44471</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44380</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44289</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44198</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44107</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44009</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43918</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43827</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43736</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43645</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43554</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43463</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>175200</v>
+      </c>
+      <c r="E8" s="3">
         <v>397900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>569600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>188700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>174000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>432400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>610900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>212800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>195100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>475600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>673600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>228100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>184800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>408900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>596500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>192400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>145000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>381300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>479900</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W8" s="3">
+      <c r="W8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="3">
         <v>123000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>298200</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
@@ -848,77 +851,80 @@
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>127500</v>
+      </c>
+      <c r="E9" s="3">
         <v>254600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>340800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>134300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>123600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>272200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>359300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>141700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>129800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>258400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>370000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>142400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>117500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>220900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>312800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>120800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>93300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>214700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>269200</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W9" s="3">
+      <c r="W9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="3">
         <v>81900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>166900</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
@@ -928,77 +934,80 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E10" s="3">
         <v>143200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>228800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>54300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>50400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>160200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>251600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>71200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>65300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>217200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>303600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>85700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>67300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>188000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>283700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>71600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>51700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>166600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>210700</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W10" s="3">
+      <c r="W10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10" s="3">
         <v>41100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>131300</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1008,8 +1017,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1038,8 +1050,9 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1118,8 +1131,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1198,38 +1214,41 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>400</v>
+      </c>
+      <c r="E14" s="3">
         <v>6900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>9700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3500</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
@@ -1240,37 +1259,37 @@
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>6400</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>1900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>7300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2300</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1278,35 +1297,38 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E15" s="3">
         <v>8700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1358,8 +1380,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1385,77 +1410,78 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>214500</v>
+      </c>
+      <c r="E17" s="3">
         <v>364500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>470700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>218500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>209400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>384100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>492800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>233900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>222100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>392500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>501500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>232100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>197300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>341800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>430100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>193000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>178100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>313300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>368300</v>
       </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W17" s="3">
+      <c r="W17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" s="3">
         <v>141600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>239300</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1465,77 +1491,80 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-39300</v>
+      </c>
+      <c r="E18" s="3">
         <v>33300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>99000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-29800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-35500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>48300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>118100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-21000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-27000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>83100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>172100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-4000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-12500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>67100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>166400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-33100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>68000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>111600</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W18" s="3">
+      <c r="W18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="3">
         <v>-18600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>58900</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1545,8 +1574,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1575,8 +1607,9 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1601,51 +1634,51 @@
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
+      <c r="K20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-200</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-400</v>
       </c>
       <c r="P20" s="3">
         <v>-400</v>
       </c>
       <c r="Q20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R20" s="3">
         <v>-800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1000</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-600</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="W20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="3">
         <v>-200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1655,77 +1688,80 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-31100</v>
+      </c>
+      <c r="E21" s="3">
         <v>42000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>107200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-22000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-27100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>56900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>126300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-12100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-18500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>91000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>179300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-3600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>74000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>171900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-26500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>76200</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X21" s="3">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y21" s="3">
         <v>86300</v>
       </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1735,77 +1771,80 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E22" s="3">
         <v>17000</v>
-      </c>
-      <c r="E22" s="3">
-        <v>18200</v>
       </c>
       <c r="F22" s="3">
         <v>18200</v>
       </c>
       <c r="G22" s="3">
+        <v>18200</v>
+      </c>
+      <c r="H22" s="3">
         <v>17100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>17200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>17700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>17200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>13400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>6800</v>
-      </c>
-      <c r="N22" s="3">
-        <v>6900</v>
       </c>
       <c r="O22" s="3">
         <v>6900</v>
       </c>
       <c r="P22" s="3">
-        <v>7400</v>
+        <v>6900</v>
       </c>
       <c r="Q22" s="3">
         <v>7400</v>
       </c>
       <c r="R22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="S22" s="3">
         <v>8100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>11500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>18600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>19500</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W22" s="3">
+      <c r="W22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X22" s="3">
         <v>22400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>23900</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1815,77 +1854,80 @@
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-55500</v>
+      </c>
+      <c r="E23" s="3">
         <v>9400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>79500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-48700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-53500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>21400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>98100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-42400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-40300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>73500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>165400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-11100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-19700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>59300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>158200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-44600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>49300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>91500</v>
       </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W23" s="3">
+      <c r="W23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X23" s="3">
         <v>-41200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>32000</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1895,77 +1937,80 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-10900</v>
+      </c>
+      <c r="E24" s="3">
         <v>19300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>18900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-14100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-14000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>25600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-10900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-10100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>42400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-3700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-5300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>14700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>39400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-3300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-14300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>7200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>19600</v>
       </c>
-      <c r="V24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W24" s="3">
+      <c r="W24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X24" s="3">
         <v>-15000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>31200</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z24" s="3" t="s">
         <v>3</v>
       </c>
@@ -1975,8 +2020,11 @@
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2055,77 +2103,80 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-44600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>60700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-34600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-39600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>16500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>72500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-31500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-30300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>57900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>123000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-7400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-14500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>44500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>118800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-30300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>42100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>71900</v>
       </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W26" s="3">
+      <c r="W26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X26" s="3">
         <v>-26200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>800</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2135,77 +2186,80 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-44600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>60700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-34600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-39600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>16500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>72500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-31500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-30300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>57900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>123000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-7400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-14500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>44500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>118800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-6500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-30300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>42100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>71900</v>
       </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W27" s="3">
+      <c r="W27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X27" s="3">
         <v>-26200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>800</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2215,8 +2269,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2295,8 +2352,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2375,8 +2435,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2455,8 +2518,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2535,8 +2601,11 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2561,51 +2630,51 @@
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
+      <c r="K32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>200</v>
-      </c>
-      <c r="O32" s="3">
-        <v>400</v>
       </c>
       <c r="P32" s="3">
         <v>400</v>
       </c>
       <c r="Q32" s="3">
+        <v>400</v>
+      </c>
+      <c r="R32" s="3">
         <v>800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1000</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>600</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="W32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="3">
         <v>200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3000</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2615,77 +2684,80 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-44600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>60700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-34600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-39600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>16500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>72500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-31500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-30300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>57900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>123000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-7400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-14500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>44500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>118800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-6500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-30300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>42100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>71900</v>
       </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W33" s="3">
+      <c r="W33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X33" s="3">
         <v>-26200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>800</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2695,8 +2767,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2775,77 +2850,80 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-44600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>60700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-34600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-39600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>16500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>72500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-31500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-30300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>57900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>123000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-7400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-14500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>44500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>118800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-6500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-30300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>42100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>71900</v>
       </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W35" s="3">
+      <c r="W35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X35" s="3">
         <v>-26200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>800</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2855,93 +2933,99 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E38" s="2">
         <v>45563</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45472</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45381</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45290</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45108</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45017</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44835</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44744</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44653</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44562</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44471</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44380</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44289</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44198</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44107</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44009</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43918</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43827</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43736</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43645</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43554</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43463</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2970,8 +3054,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3000,68 +3085,69 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E41" s="3">
         <v>108500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>74400</v>
-      </c>
-      <c r="F41" s="3">
-        <v>8400</v>
       </c>
       <c r="G41" s="3">
         <v>8400</v>
       </c>
       <c r="H41" s="3">
+        <v>8400</v>
+      </c>
+      <c r="I41" s="3">
         <v>55400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>19400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>112300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>193100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>52000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>53300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>343500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>309100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>88700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>102800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>157100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>148900</v>
       </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3080,8 +3166,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3160,68 +3249,71 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>29800</v>
+      </c>
+      <c r="E43" s="3">
         <v>45500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>48200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>34400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>22500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>29400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>49300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>60400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>46400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>45300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>47300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>44200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>39400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>77700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>47800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>94500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>74200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>31500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>35800</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3240,68 +3332,71 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>271100</v>
+      </c>
+      <c r="E44" s="3">
         <v>234300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>302200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>379100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>334000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>311800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>436600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>492300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>429500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>361700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>361400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>345000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>244600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>198800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>224500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>277900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>174500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>149000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>181100</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3320,68 +3415,71 @@
       <c r="AB44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E45" s="3">
         <v>9400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>5900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>29900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>23100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>30500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>30700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>38200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>41100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>28600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>87300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>65500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>22700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>24600</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3400,68 +3498,71 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>341600</v>
+      </c>
+      <c r="E46" s="3">
         <v>422400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>457000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>453600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>392000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>420300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>536700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>591700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>508500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>542400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>632300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>471900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>375500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>601700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>610100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>448300</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>340100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>360200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>390400</v>
       </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3480,8 +3581,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3506,8 +3610,8 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -3560,68 +3664,71 @@
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>356900</v>
+      </c>
+      <c r="E48" s="3">
         <v>368900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>376700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>350000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>330700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>341700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>335800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>312000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>308900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>314600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>293300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>279100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>273200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>282600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>235400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>245200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>253800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>244000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>74700</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3640,68 +3747,71 @@
       <c r="AB48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>214200</v>
+      </c>
+      <c r="E49" s="3">
         <v>215100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>216000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>217000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>217900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>218900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>219800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>216600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>218100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>213700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>155700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>146900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>132400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>129000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>127700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>128600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>121200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>122000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>121700</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3720,8 +3830,11 @@
       <c r="AB49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3800,8 +3913,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3880,68 +3996,71 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>38200</v>
+      </c>
+      <c r="E52" s="3">
         <v>39700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>40000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>40300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>41900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>46000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>44900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>42900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>41300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>39000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>35700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>32400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>30200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>28900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>24600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>35900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>31400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>21000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1200</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3960,8 +4079,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4040,68 +4162,71 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>967000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1050300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1105200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1095200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>998500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1034400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1137400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1163200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1076800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1109600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1117000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>930200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>811300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1042200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>997800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>857300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>745800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>746400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>588000</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4120,8 +4245,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4150,8 +4278,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4180,68 +4309,69 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E57" s="3">
         <v>67600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>108900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>112400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>63500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>58600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>147400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>139800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>117300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>156500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>219000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>160900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>99500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>101000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>155500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>181500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>69000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>92400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>133100</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4260,34 +4390,37 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>65100</v>
+      </c>
+      <c r="E58" s="3">
         <v>71800</v>
-      </c>
-      <c r="E58" s="3">
-        <v>69700</v>
       </c>
       <c r="F58" s="3">
         <v>69700</v>
       </c>
       <c r="G58" s="3">
+        <v>69700</v>
+      </c>
+      <c r="H58" s="3">
         <v>71200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>70900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>69400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>69700</v>
-      </c>
-      <c r="K58" s="3">
-        <v>8100</v>
       </c>
       <c r="L58" s="3">
         <v>8100</v>
@@ -4311,7 +4444,7 @@
         <v>8100</v>
       </c>
       <c r="S58" s="3">
-        <v>8300</v>
+        <v>8100</v>
       </c>
       <c r="T58" s="3">
         <v>8300</v>
@@ -4319,8 +4452,8 @@
       <c r="U58" s="3">
         <v>8300</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
+      <c r="V58" s="3">
+        <v>8300</v>
       </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
@@ -4340,68 +4473,71 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E59" s="3">
         <v>12700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>19900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>129200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>183400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>205800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>169200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>146600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>200700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>190500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>136100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>114200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>157500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>119300</v>
       </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4420,68 +4556,71 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>194000</v>
+      </c>
+      <c r="E60" s="3">
         <v>246900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>285900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>262100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>204600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>225800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>315300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>292400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>254600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>348000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>432900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>338200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>254200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>309700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>354100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>325800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>191600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>258200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>260700</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4500,68 +4639,71 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>988500</v>
+      </c>
+      <c r="E61" s="3">
         <v>978300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>985400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1061000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>989100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>966500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>998900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1122100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>869100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>779700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>781300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>827900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>784500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>160000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>787700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>789300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>795400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1179600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1182800</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4580,68 +4722,71 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4600</v>
+      </c>
+      <c r="E62" s="3">
         <v>2300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3100</v>
-      </c>
-      <c r="G62" s="3">
-        <v>3500</v>
       </c>
       <c r="H62" s="3">
         <v>3500</v>
       </c>
       <c r="I62" s="3">
-        <v>3100</v>
+        <v>3500</v>
       </c>
       <c r="J62" s="3">
         <v>3100</v>
       </c>
       <c r="K62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="L62" s="3">
         <v>178700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>179900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>161500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>149800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>153800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>790000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>121700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>133200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>145300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>135700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>13600</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4660,8 +4805,11 @@
       <c r="AB62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4740,8 +4888,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4820,8 +4971,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4900,68 +5054,71 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1187000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1227500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1273300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1326200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1197200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1195800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1317200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1418200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1302400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1307600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1375800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1315900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1192600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1259800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1263500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1248300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1132300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1573400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1457100</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
@@ -4980,8 +5137,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5010,8 +5170,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5090,8 +5251,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5170,8 +5334,11 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5250,8 +5417,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5330,68 +5500,71 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-328800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-284200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-274300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-334900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-300400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-260800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-277300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-349900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-318300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-288100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-346000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-469000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-461500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-422500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-467000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-585800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-386600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-827200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-869200</v>
       </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5410,8 +5583,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5490,8 +5666,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5570,8 +5749,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5650,68 +5832,71 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-220000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-177100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-168200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-231000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-198600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-161400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-179800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-255000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-225600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-198000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-258800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-385700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-381300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-217600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-265700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-391000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-386400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-827000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-869100</v>
       </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5730,8 +5915,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5810,162 +5998,168 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E80" s="2">
         <v>45563</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45472</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45381</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45290</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45108</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45017</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44835</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44744</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44653</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44562</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44471</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44380</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44289</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44198</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44107</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44009</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43918</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43827</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43736</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43645</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43554</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43463</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-44600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>60700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-34600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-39600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>16500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>72500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-31500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-30300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>57900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>123000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-7400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-14500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>44500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>118800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-6500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-30300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>42100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>71900</v>
       </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="W81" s="3">
+      <c r="W81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X81" s="3">
         <v>-26200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>800</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
@@ -5975,8 +6169,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6005,65 +6202,66 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E83" s="3">
         <v>7700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>6900</v>
-      </c>
-      <c r="F83" s="3">
-        <v>7600</v>
       </c>
       <c r="G83" s="3">
         <v>7600</v>
       </c>
       <c r="H83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="I83" s="3">
         <v>7000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>8500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>9200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7300</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>6300</v>
       </c>
       <c r="R83" s="3">
         <v>6300</v>
       </c>
       <c r="S83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="T83" s="3">
         <v>6600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>8300</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6076,8 +6274,8 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
@@ -6085,8 +6283,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6165,8 +6366,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6245,8 +6449,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6325,8 +6532,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6405,8 +6615,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6485,65 +6698,68 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-105100</v>
+      </c>
+      <c r="E89" s="3">
         <v>47100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>175500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-43200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-71900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>81300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>171200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-61600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-184400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-6000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>209400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-11200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-125600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>51200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>229800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>7800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-119300</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>17500</v>
       </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6556,8 +6772,8 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z89" s="3">
-        <v>0</v>
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA89" s="3">
         <v>0</v>
@@ -6565,8 +6781,11 @@
       <c r="AB89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6595,65 +6814,66 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5100</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6666,8 +6886,8 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
@@ -6675,8 +6895,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6755,8 +6978,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6835,65 +7061,68 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-17300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-72800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-22300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-33400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-13200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-9100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5100</v>
       </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
@@ -6906,8 +7135,8 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
@@ -6915,8 +7144,11 @@
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6945,8 +7177,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6971,8 +7204,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -7025,8 +7258,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7105,8 +7341,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7185,8 +7424,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7265,65 +7507,68 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-99200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>56500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>35500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-33700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-143100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>77400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>88600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-46000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>43200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-154100</v>
-      </c>
-      <c r="P100" s="3">
-        <v>-2000</v>
       </c>
       <c r="Q100" s="3">
         <v>-2000</v>
       </c>
       <c r="R100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="S100" s="3">
         <v>-8800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>66600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-4200</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7336,8 +7581,8 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA100" s="3">
         <v>0</v>
@@ -7345,8 +7590,11 @@
       <c r="AB100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7371,8 +7619,8 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -7425,65 +7673,68 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-96900</v>
+      </c>
+      <c r="E102" s="3">
         <v>34100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>66000</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
       <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-47000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>36000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>6000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-109600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-80800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>141200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-290200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>36000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>218700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-13700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-53000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8200</v>
       </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7496,13 +7747,16 @@
       <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
+      <c r="Z102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA102" s="3">
         <v>0</v>
       </c>
       <c r="AB102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LESL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LESL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
   <si>
     <t>LESL</t>
   </si>
@@ -656,195 +656,199 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
         <v>45654</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45563</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45472</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45381</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45290</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45108</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45017</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44835</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44744</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44653</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44562</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44471</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44380</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44289</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44198</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44107</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44009</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43918</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43827</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43736</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43645</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43554</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43463</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>177100</v>
+      </c>
+      <c r="E8" s="3">
         <v>175200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>397900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>569600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>188700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>174000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>432400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>610900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>212800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>195100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>475600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>673600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>228100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>184800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>408900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>596500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>192400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>145000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>381300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>479900</v>
       </c>
-      <c r="W8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X8" s="3">
+      <c r="X8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="3">
         <v>123000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>298200</v>
       </c>
-      <c r="Z8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
@@ -854,80 +858,83 @@
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>133200</v>
+      </c>
+      <c r="E9" s="3">
         <v>127500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>254600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>340800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>134300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>123600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>272200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>359300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>141700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>129800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>258400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>370000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>142400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>117500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>220900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>312800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>120800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>93300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>214700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>269200</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X9" s="3">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y9" s="3">
         <v>81900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>166900</v>
       </c>
-      <c r="Z9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
@@ -937,80 +944,83 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E10" s="3">
         <v>47700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>143200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>228800</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>54300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>50400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>160200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>251600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>71200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>65300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>217200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>303600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>85700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>67300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>188000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>283700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>71600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>51700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>166600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>210700</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X10" s="3">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y10" s="3">
         <v>41100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>131300</v>
       </c>
-      <c r="Z10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1020,8 +1030,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1051,8 +1064,9 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1134,8 +1148,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1217,41 +1234,44 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E14" s="3">
         <v>400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>9700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3500</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
@@ -1262,37 +1282,37 @@
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>6400</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>1900</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>7300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>2300</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1300,38 +1320,41 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E15" s="3">
         <v>8200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>7800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8900</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1383,8 +1406,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1411,80 +1437,81 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>223400</v>
+      </c>
+      <c r="E17" s="3">
         <v>214500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>364500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>470700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>218500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>209400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>384100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>492800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>233900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>222100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>392500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>501500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>232100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>197300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>341800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>430100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>193000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>178100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>313300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>368300</v>
       </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X17" s="3">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y17" s="3">
         <v>141600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>239300</v>
       </c>
-      <c r="Z17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1494,80 +1521,83 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-46300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-39300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>33300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>99000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-29800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-35500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>48300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>118100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-21000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-27000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>83100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>172100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-12500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>67100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>166400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-33100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>68000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>111600</v>
       </c>
-      <c r="W18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X18" s="3">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-18600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>58900</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1577,8 +1607,11 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1608,8 +1641,9 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1637,51 +1671,51 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-400</v>
       </c>
       <c r="Q20" s="3">
         <v>-400</v>
       </c>
       <c r="R20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="S20" s="3">
         <v>-800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1000</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>-200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-600</v>
       </c>
-      <c r="W20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X20" s="3">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1691,80 +1725,83 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-31100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>42000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>107200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-22000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-27100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>56900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>126300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-12100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-18500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>91000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>179300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>2400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-3600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>74000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>171900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-26500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>76200</v>
       </c>
-      <c r="V21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z21" s="3">
         <v>86300</v>
       </c>
-      <c r="Z21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1774,80 +1811,83 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E22" s="3">
         <v>15800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17000</v>
-      </c>
-      <c r="F22" s="3">
-        <v>18200</v>
       </c>
       <c r="G22" s="3">
         <v>18200</v>
       </c>
       <c r="H22" s="3">
+        <v>18200</v>
+      </c>
+      <c r="I22" s="3">
         <v>17100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>17200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>17700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>17200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>9600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>6800</v>
-      </c>
-      <c r="O22" s="3">
-        <v>6900</v>
       </c>
       <c r="P22" s="3">
         <v>6900</v>
       </c>
       <c r="Q22" s="3">
-        <v>7400</v>
+        <v>6900</v>
       </c>
       <c r="R22" s="3">
         <v>7400</v>
       </c>
       <c r="S22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="T22" s="3">
         <v>8100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>11500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>18600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>19500</v>
       </c>
-      <c r="W22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X22" s="3">
+      <c r="X22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y22" s="3">
         <v>22400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>23900</v>
       </c>
-      <c r="Z22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1857,80 +1897,83 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-64300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-55500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>9400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>79500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-48700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-53500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>21400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>98100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-42400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-40300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>73500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>165400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-11100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-19700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>59300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>158200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-9800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-44600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>49300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>91500</v>
       </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X23" s="3">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="3">
         <v>-41200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>32000</v>
       </c>
-      <c r="Z23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1940,80 +1983,83 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-10900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>19300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>18900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-14100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-14000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>25600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-10900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-10100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>15600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>42400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>14700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>39400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-3300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-14300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>19600</v>
       </c>
-      <c r="W24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X24" s="3">
+      <c r="X24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y24" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>31200</v>
       </c>
-      <c r="Z24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2023,8 +2069,11 @@
       <c r="AC24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2106,80 +2155,83 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-51300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-44600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-9900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>60700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-34600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-39600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>16500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>72500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-31500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-30300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>57900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>123000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-7400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>44500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>118800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-6500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-30300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>42100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>71900</v>
       </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X26" s="3">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y26" s="3">
         <v>-26200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>800</v>
       </c>
-      <c r="Z26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2189,80 +2241,83 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-51300</v>
+      </c>
+      <c r="E27" s="3">
         <v>-44600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-9900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>60700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-34600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-39600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>16500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>72500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-31500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-30300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>57900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>123000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-7400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>44500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>118800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-30300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>42100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>71900</v>
       </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X27" s="3">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y27" s="3">
         <v>-26200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>800</v>
       </c>
-      <c r="Z27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2272,8 +2327,11 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2355,8 +2413,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2438,8 +2499,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2521,8 +2585,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2604,8 +2671,11 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2633,51 +2703,51 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>400</v>
       </c>
       <c r="Q32" s="3">
         <v>400</v>
       </c>
       <c r="R32" s="3">
+        <v>400</v>
+      </c>
+      <c r="S32" s="3">
         <v>800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1000</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>600</v>
       </c>
-      <c r="W32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X32" s="3">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3000</v>
       </c>
-      <c r="Z32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2687,80 +2757,83 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-51300</v>
+      </c>
+      <c r="E33" s="3">
         <v>-44600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-9900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>60700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-34600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-39600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>16500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>72500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-31500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-30300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>57900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>123000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-7400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>44500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>118800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-30300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>42100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>71900</v>
       </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X33" s="3">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y33" s="3">
         <v>-26200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>800</v>
       </c>
-      <c r="Z33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2770,8 +2843,11 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2853,80 +2929,83 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-51300</v>
+      </c>
+      <c r="E35" s="3">
         <v>-44600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-9900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>60700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-34600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-39600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>16500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>72500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-31500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-30300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>57900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>123000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-7400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>44500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>118800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-30300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>42100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>71900</v>
       </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X35" s="3">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y35" s="3">
         <v>-26200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>800</v>
       </c>
-      <c r="Z35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
@@ -2936,96 +3015,102 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
         <v>45654</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45563</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45472</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45381</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45290</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45108</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45017</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44835</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44744</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44653</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44562</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44471</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44380</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44289</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44198</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44107</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44009</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43918</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43827</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43736</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43645</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43554</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43463</v>
       </c>
-      <c r="AC38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3055,8 +3140,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3086,71 +3172,72 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>17300</v>
+      </c>
+      <c r="E41" s="3">
         <v>11600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>108500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>74400</v>
-      </c>
-      <c r="G41" s="3">
-        <v>8400</v>
       </c>
       <c r="H41" s="3">
         <v>8400</v>
       </c>
       <c r="I41" s="3">
+        <v>8400</v>
+      </c>
+      <c r="J41" s="3">
         <v>55400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>19400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>8700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>112300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>193100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>52000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>53300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>343500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>309100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>88700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>102800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>157100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>148900</v>
       </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3169,8 +3256,11 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3252,71 +3342,74 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E43" s="3">
         <v>29800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>45500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>48200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>34400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>22500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>29400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>49300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>60400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>46400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>45300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>47300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>44200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>39400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>77700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>47800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>94500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>74200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>31500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>35800</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3335,71 +3428,74 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>335100</v>
+      </c>
+      <c r="E44" s="3">
         <v>271100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>234300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>302200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>379100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>334000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>311800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>436600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>492300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>429500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>361700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>361400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>345000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>244600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>198800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>224500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>277900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>174500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>149000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>181100</v>
       </c>
-      <c r="W44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3418,71 +3514,74 @@
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E45" s="3">
         <v>9600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>13000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>5900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>29900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>23100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>30500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>30700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>38200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>41100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>28600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>87300</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>65500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>22700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>24600</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3501,71 +3600,74 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>417600</v>
+      </c>
+      <c r="E46" s="3">
         <v>341600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>422400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>457000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>453600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>392000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>420300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>536700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>591700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>508500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>542400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>632300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>471900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>375500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>601700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>610100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>448300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>340100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>360200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>390400</v>
       </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3584,8 +3686,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3613,8 +3718,8 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -3667,71 +3772,74 @@
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>346400</v>
+      </c>
+      <c r="E48" s="3">
         <v>356900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>368900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>376700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>350000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>330700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>341700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>335800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>312000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>308900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>314600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>293300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>279100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>273200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>282600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>235400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>245200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>253800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>244000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>74700</v>
       </c>
-      <c r="W48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3750,71 +3858,74 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>213300</v>
+      </c>
+      <c r="E49" s="3">
         <v>214200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>215100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>216000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>217000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>217900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>218900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>219800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>216600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>218100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>213700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>155700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>146900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>132400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>129000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>127700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>128600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>121200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>122000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>121700</v>
       </c>
-      <c r="W49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3833,8 +3944,11 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3916,8 +4030,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3999,71 +4116,74 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E52" s="3">
         <v>38200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>39700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>40000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>40300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>41900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>46000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>44900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>42900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>41300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>39000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>35700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>32400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>30200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>28900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>24600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>35900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>31400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>21000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1200</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4082,8 +4202,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4165,71 +4288,74 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1043000</v>
+      </c>
+      <c r="E54" s="3">
         <v>967000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1050300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1105200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1095200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>998500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1034400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1137400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1163200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1076800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1109600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1117000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>930200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>811300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1042200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>997800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>857300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>745800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>746400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>588000</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4248,8 +4374,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4279,8 +4408,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4310,71 +4440,72 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>114800</v>
+      </c>
+      <c r="E57" s="3">
         <v>56200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>67600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>108900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>112400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>63500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>58600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>147400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>139800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>117300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>156500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>219000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>160900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>99500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>101000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>155500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>181500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>69000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>92400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>133100</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4393,37 +4524,40 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>64500</v>
+      </c>
+      <c r="E58" s="3">
         <v>65100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>71800</v>
-      </c>
-      <c r="F58" s="3">
-        <v>69700</v>
       </c>
       <c r="G58" s="3">
         <v>69700</v>
       </c>
       <c r="H58" s="3">
+        <v>69700</v>
+      </c>
+      <c r="I58" s="3">
         <v>71200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>70900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>69400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>69700</v>
-      </c>
-      <c r="L58" s="3">
-        <v>8100</v>
       </c>
       <c r="M58" s="3">
         <v>8100</v>
@@ -4447,7 +4581,7 @@
         <v>8100</v>
       </c>
       <c r="T58" s="3">
-        <v>8300</v>
+        <v>8100</v>
       </c>
       <c r="U58" s="3">
         <v>8300</v>
@@ -4455,8 +4589,8 @@
       <c r="V58" s="3">
         <v>8300</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
+      <c r="W58" s="3">
+        <v>8300</v>
       </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
@@ -4476,71 +4610,74 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E59" s="3">
         <v>12400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>19900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>16800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>129200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>183400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>205800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>169200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>146600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>200700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>190500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>136100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>114200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>157500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>119300</v>
       </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4559,71 +4696,74 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>267600</v>
+      </c>
+      <c r="E60" s="3">
         <v>194000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>246900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>285900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>262100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>204600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>225800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>315300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>292400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>254600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>348000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>432900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>338200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>254200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>309700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>354100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>325800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>191600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>258200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>260700</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4642,71 +4782,74 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1040800</v>
+      </c>
+      <c r="E61" s="3">
         <v>988500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>978300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>985400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1061000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>989100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>966500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>998900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1122100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>869100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>779700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>781300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>827900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>784500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>160000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>787700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>789300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>795400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1179600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1182800</v>
       </c>
-      <c r="W61" s="3">
-        <v>0</v>
-      </c>
       <c r="X61" s="3">
         <v>0</v>
       </c>
@@ -4725,71 +4868,74 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E62" s="3">
         <v>4600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>2300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>3100</v>
-      </c>
-      <c r="H62" s="3">
-        <v>3500</v>
       </c>
       <c r="I62" s="3">
         <v>3500</v>
       </c>
       <c r="J62" s="3">
-        <v>3100</v>
+        <v>3500</v>
       </c>
       <c r="K62" s="3">
         <v>3100</v>
       </c>
       <c r="L62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="M62" s="3">
         <v>178700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>179900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>161500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>149800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>153800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>790000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>121700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>133200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>145300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>135700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>13600</v>
       </c>
-      <c r="W62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4808,8 +4954,11 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4891,8 +5040,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4974,8 +5126,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5057,71 +5212,74 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1312400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1187000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1227500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1273300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1326200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1197200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1195800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1317200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1418200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1302400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1307600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1375800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1315900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1192600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1259800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1263500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1248300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1132300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1573400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1457100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5140,8 +5298,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5171,8 +5332,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5254,8 +5416,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5337,8 +5502,11 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5420,8 +5588,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5503,71 +5674,74 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-380100</v>
+      </c>
+      <c r="E72" s="3">
         <v>-328800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-284200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-274300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-334900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-300400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-260800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-277300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-349900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-318300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-288100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-346000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-469000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-461500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-422500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-467000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-585800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-386600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-827200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-869200</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5586,8 +5760,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5669,8 +5846,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5752,8 +5932,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5835,71 +6018,74 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-269500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-220000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-177100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-168200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-231000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-198600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-161400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-179800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-255000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-225600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-198000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-258800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-385700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-381300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-217600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-265700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-391000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-386400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-827000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-869100</v>
       </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
@@ -5918,8 +6104,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6001,168 +6190,174 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
         <v>45654</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45563</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45472</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45381</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45290</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45108</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45017</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44835</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44744</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44653</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44562</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44471</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44380</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44289</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44198</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44107</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44009</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43918</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43827</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43736</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43645</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43554</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43463</v>
       </c>
-      <c r="AC80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-51300</v>
+      </c>
+      <c r="E81" s="3">
         <v>-44600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-9900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>60700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-34600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-39600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>16500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>72500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-31500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-30300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>57900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>123000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-7400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-14500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>44500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>118800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-30300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>42100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>71900</v>
       </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="X81" s="3">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y81" s="3">
         <v>-26200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>800</v>
       </c>
-      <c r="Z81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6172,8 +6367,11 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6203,68 +6401,69 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E83" s="3">
         <v>7400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6900</v>
-      </c>
-      <c r="G83" s="3">
-        <v>7600</v>
       </c>
       <c r="H83" s="3">
         <v>7600</v>
       </c>
       <c r="I83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="J83" s="3">
         <v>7000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>8500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>9200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>7300</v>
-      </c>
-      <c r="R83" s="3">
-        <v>6300</v>
       </c>
       <c r="S83" s="3">
         <v>6300</v>
       </c>
       <c r="T83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="U83" s="3">
         <v>6600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>8300</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6277,8 +6476,8 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -6286,8 +6485,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6369,8 +6571,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6452,8 +6657,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6535,8 +6743,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6618,8 +6829,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6701,68 +6915,71 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-49200</v>
+      </c>
+      <c r="E89" s="3">
         <v>-105100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>47100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>175500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-43200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-71900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>81300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>171200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-61600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-184400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-6000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>209400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-11200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-125600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>51200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>229800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>7800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-119300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>17500</v>
       </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6775,8 +6992,8 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA89" s="3">
-        <v>0</v>
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB89" s="3">
         <v>0</v>
@@ -6784,8 +7001,11 @@
       <c r="AC89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6815,68 +7035,69 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-10300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-13300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-6800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5100</v>
       </c>
-      <c r="V91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6889,8 +7110,8 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -6898,8 +7119,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6981,8 +7205,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7064,68 +7291,71 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-17300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-13700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-72800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-22300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-33400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-13200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-9100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5100</v>
       </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7138,8 +7368,8 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB94" s="3">
         <v>0</v>
@@ -7147,8 +7377,11 @@
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7178,8 +7411,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7207,8 +7441,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7261,8 +7495,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7344,8 +7581,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7427,8 +7667,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7510,68 +7753,71 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>61300</v>
+      </c>
+      <c r="E100" s="3">
         <v>12800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-99200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>56500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>35500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-33700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-143100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>77400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>88600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-46000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>43200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-154100</v>
-      </c>
-      <c r="Q100" s="3">
-        <v>-2000</v>
       </c>
       <c r="R100" s="3">
         <v>-2000</v>
       </c>
       <c r="S100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="T100" s="3">
         <v>-8800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>66600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4200</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7584,8 +7830,8 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB100" s="3">
         <v>0</v>
@@ -7593,8 +7839,11 @@
       <c r="AC100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7622,8 +7871,8 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -7676,68 +7925,71 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-96900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>34100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>66000</v>
       </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
         <v>-47000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>36000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>10700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>6000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-109600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-80800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>141200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-290200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>36000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>218700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-13700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-53000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>8200</v>
       </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
       </c>
@@ -7750,13 +8002,16 @@
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
+      <c r="AA102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB102" s="3">
         <v>0</v>
       </c>
       <c r="AC102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LESL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LESL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="92">
   <si>
     <t>LESL</t>
   </si>
@@ -656,202 +656,206 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AD102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45654</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45472</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45290</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45108</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45017</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44835</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44744</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44653</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44562</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44471</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44380</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44289</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44198</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44107</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44009</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43918</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43827</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43736</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43645</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43554</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43463</v>
       </c>
-      <c r="AD7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>500300</v>
+      </c>
+      <c r="E8" s="3">
         <v>177100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>175200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>397900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>569600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>188700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>174000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>432400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>610900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>212800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>195100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>475600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>673600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>228100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>184800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>408900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>596500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>192400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>145000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>381300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>479900</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y8" s="3">
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="3">
         <v>123000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>298200</v>
       </c>
-      <c r="AA8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB8" s="3" t="s">
         <v>3</v>
       </c>
@@ -861,83 +865,86 @@
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>302500</v>
+      </c>
+      <c r="E9" s="3">
         <v>133200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>127500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>254600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>340800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>134300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>123600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>272200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>359300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>141700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>129800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>258400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>370000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>142400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>117500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>220900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>312800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>120800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>93300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>214700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>269200</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y9" s="3">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="3">
         <v>81900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>166900</v>
       </c>
-      <c r="AA9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
@@ -947,83 +954,86 @@
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>197900</v>
+      </c>
+      <c r="E10" s="3">
         <v>43900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>47700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>143200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>228800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>54300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>50400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>160200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>251600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>71200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>65300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>217200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>303600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>85700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>67300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>188000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>283700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>71600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>51700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>166600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>210700</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y10" s="3">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="3">
         <v>41100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>131300</v>
       </c>
-      <c r="AA10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1033,8 +1043,11 @@
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1065,8 +1078,9 @@
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1151,8 +1165,11 @@
       <c r="AD12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1237,44 +1254,47 @@
       <c r="AD13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E14" s="3">
         <v>2100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>9700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3500</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
@@ -1285,37 +1305,37 @@
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>6400</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>1900</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>7300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2300</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>3</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1323,41 +1343,44 @@
       <c r="AD14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E15" s="3">
         <v>8300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>8200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>8700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>8600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8900</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1409,8 +1432,11 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1438,83 +1464,84 @@
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
-    </row>
-    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>428900</v>
+      </c>
+      <c r="E17" s="3">
         <v>223400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>214500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>364500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>470700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>218500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>209400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>384100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>492800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>233900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>222100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>392500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>501500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>232100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>197300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>341800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>430100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>193000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>178100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>313300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>368300</v>
       </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y17" s="3">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z17" s="3">
         <v>141600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>239300</v>
       </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1524,83 +1551,86 @@
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>71400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-46300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-39300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>33300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>99000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-29800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-35500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>48300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>118100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-21000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-27000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>83100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>172100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-12500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>67100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>166400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-33100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>68000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>111600</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y18" s="3">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="3">
         <v>-18600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>58900</v>
       </c>
-      <c r="AA18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1610,8 +1640,11 @@
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1642,8 +1675,9 @@
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
-    </row>
-    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1674,51 +1708,51 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
+      <c r="M20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>-400</v>
       </c>
       <c r="R20" s="3">
         <v>-400</v>
       </c>
       <c r="S20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="T20" s="3">
         <v>-800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1000</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-600</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y20" s="3">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1728,83 +1762,86 @@
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-38000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-31100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>42000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>107200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-22000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-27100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>56900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>126300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-12100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-18500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>91000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>179300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-3600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>74000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>171900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>4600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-26500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>76200</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="3">
         <v>86300</v>
       </c>
-      <c r="AA21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1814,83 +1851,86 @@
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>15800</v>
+      </c>
+      <c r="E22" s="3">
         <v>15900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>15800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>18200</v>
       </c>
       <c r="H22" s="3">
         <v>18200</v>
       </c>
       <c r="I22" s="3">
+        <v>18200</v>
+      </c>
+      <c r="J22" s="3">
         <v>17100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>17200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>17700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>17200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>9600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>6800</v>
-      </c>
-      <c r="P22" s="3">
-        <v>6900</v>
       </c>
       <c r="Q22" s="3">
         <v>6900</v>
       </c>
       <c r="R22" s="3">
-        <v>7400</v>
+        <v>6900</v>
       </c>
       <c r="S22" s="3">
         <v>7400</v>
       </c>
       <c r="T22" s="3">
+        <v>7400</v>
+      </c>
+      <c r="U22" s="3">
         <v>8100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>11500</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>18600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>19500</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y22" s="3">
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z22" s="3">
         <v>22400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>23900</v>
       </c>
-      <c r="AA22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1900,83 +1940,86 @@
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>52600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-64300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-55500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>9400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>79500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-48700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-53500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>21400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>98100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-42400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-40300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>73500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>165400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-11100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-19700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>59300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>158200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-9800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-44600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>49300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>91500</v>
       </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y23" s="3">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z23" s="3">
         <v>-41200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>32000</v>
       </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1986,83 +2029,86 @@
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-13000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-10900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>19300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>18900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-14100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-14000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>25600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-10900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-10100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>15600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>42400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-5300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>14700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>39400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-3300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-14300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>19600</v>
       </c>
-      <c r="X24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y24" s="3">
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z24" s="3">
         <v>-15000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>31200</v>
       </c>
-      <c r="AA24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB24" s="3" t="s">
         <v>3</v>
       </c>
@@ -2072,8 +2118,11 @@
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2158,83 +2207,86 @@
       <c r="AD25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-51300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-44600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-9900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>60700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-34600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-39600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>16500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>72500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-31500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-30300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>57900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>123000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-14500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>44500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>118800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-6500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-30300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>42100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>71900</v>
       </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y26" s="3">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-26200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>800</v>
       </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
@@ -2244,83 +2296,86 @@
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-51300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-44600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-9900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>60700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-34600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-39600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>16500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>72500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-31500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-30300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>57900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>123000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-14500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>44500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>118800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-30300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>42100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>71900</v>
       </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y27" s="3">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z27" s="3">
         <v>-26200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>800</v>
       </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
@@ -2330,8 +2385,11 @@
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2416,8 +2474,11 @@
       <c r="AD28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2502,8 +2563,11 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2588,8 +2652,11 @@
       <c r="AD30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2674,8 +2741,11 @@
       <c r="AD31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2706,51 +2776,51 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
+      <c r="M32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>400</v>
       </c>
       <c r="R32" s="3">
         <v>400</v>
       </c>
       <c r="S32" s="3">
+        <v>400</v>
+      </c>
+      <c r="T32" s="3">
         <v>800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1000</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>600</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y32" s="3">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="3">
         <v>200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3000</v>
       </c>
-      <c r="AA32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2760,83 +2830,86 @@
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-51300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-44600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-9900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>60700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-34600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-39600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>16500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>72500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-31500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-30300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>57900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>123000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-14500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>44500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>118800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-30300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>42100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>71900</v>
       </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y33" s="3">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z33" s="3">
         <v>-26200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>800</v>
       </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
@@ -2846,8 +2919,11 @@
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2932,83 +3008,86 @@
       <c r="AD34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-51300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-44600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-9900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>60700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-34600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-39600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>16500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>72500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-31500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-30300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>57900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>123000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-14500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>44500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>118800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-30300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>42100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>71900</v>
       </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y35" s="3">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z35" s="3">
         <v>-26200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>800</v>
       </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
@@ -3018,99 +3097,105 @@
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45654</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45472</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45290</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45108</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45017</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44835</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44744</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44653</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44562</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44471</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44380</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44289</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44198</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44107</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44009</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43918</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43827</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43736</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43645</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43554</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43463</v>
       </c>
-      <c r="AD38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3141,8 +3226,9 @@
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
-    </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3173,74 +3259,75 @@
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
-    </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>42700</v>
+      </c>
+      <c r="E41" s="3">
         <v>17300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>108500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>74400</v>
-      </c>
-      <c r="H41" s="3">
-        <v>8400</v>
       </c>
       <c r="I41" s="3">
         <v>8400</v>
       </c>
       <c r="J41" s="3">
+        <v>8400</v>
+      </c>
+      <c r="K41" s="3">
         <v>55400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>19400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>8700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>112300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>193100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>52000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>53300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>343500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>309100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>88700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>102800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>157100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>148900</v>
       </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3259,8 +3346,11 @@
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3345,74 +3435,77 @@
       <c r="AD42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>34800</v>
+      </c>
+      <c r="E43" s="3">
         <v>32000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>29800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>45500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>48200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>34400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>22500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>29400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>49300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>60400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>46400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>45300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>47300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>44200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>39400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>77700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>47800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>94500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>74200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>31500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>35800</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3431,74 +3524,77 @@
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>273200</v>
+      </c>
+      <c r="E44" s="3">
         <v>335100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>271100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>234300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>302200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>379100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>334000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>311800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>436600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>492300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>429500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>361700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>361400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>345000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>244600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>198800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>224500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>277900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>174500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>149000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>181100</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3517,74 +3613,77 @@
       <c r="AD44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12900</v>
+      </c>
+      <c r="E45" s="3">
         <v>13500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>9600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>29900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>23100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>30500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>30700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>38200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>41100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>28600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>87300</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>65500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>22700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>24600</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3603,74 +3702,77 @@
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>385100</v>
+      </c>
+      <c r="E46" s="3">
         <v>417600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>341600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>422400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>457000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>453600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>392000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>420300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>536700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>591700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>508500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>542400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>632300</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>471900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>375500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>601700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>610100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>448300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>340100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>360200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>390400</v>
       </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3689,8 +3791,11 @@
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3721,8 +3826,8 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -3775,74 +3880,77 @@
       <c r="AD47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>355100</v>
+      </c>
+      <c r="E48" s="3">
         <v>346400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>356900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>368900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>376700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>350000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>330700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>341700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>335800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>312000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>308900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>314600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>293300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>279100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>273200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>282600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>235400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>245200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>253800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>244000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>74700</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3861,74 +3969,77 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>212400</v>
+      </c>
+      <c r="E49" s="3">
         <v>213300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>214200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>215100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>216000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>217000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>217900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>218900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>219800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>216600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>218100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>213700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>155700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>146900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>132400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>129000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>127700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>128600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>121200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>122000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>121700</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
@@ -3947,8 +4058,11 @@
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4033,8 +4147,11 @@
       <c r="AD50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4119,74 +4236,77 @@
       <c r="AD51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E52" s="3">
         <v>36500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>38200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>39700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>40000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>40300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>41900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>46000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>44900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>42900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>41300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>39000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>35700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>32400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>30200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>28900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>24600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>35900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>31400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>21000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1200</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4205,8 +4325,11 @@
       <c r="AD52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4291,74 +4414,77 @@
       <c r="AD53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>989500</v>
+      </c>
+      <c r="E54" s="3">
         <v>1043000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>967000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1050300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1105200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1095200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>998500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1034400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1137400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1163200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1076800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1109600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1117000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>930200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>811300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1042200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>997800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>857300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>745800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>746400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>588000</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4377,8 +4503,11 @@
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4409,8 +4538,9 @@
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
-    </row>
-    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4441,74 +4571,75 @@
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
-    </row>
-    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>91600</v>
+      </c>
+      <c r="E57" s="3">
         <v>114800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>56200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>67600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>108900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>112400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>63500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>58600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>147400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>139800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>117300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>156500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>219000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>160900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>99500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>101000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>155500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>181500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>69000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>92400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>133100</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4527,40 +4658,43 @@
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>65800</v>
+      </c>
+      <c r="E58" s="3">
         <v>64500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>65100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>71800</v>
-      </c>
-      <c r="G58" s="3">
-        <v>69700</v>
       </c>
       <c r="H58" s="3">
         <v>69700</v>
       </c>
       <c r="I58" s="3">
+        <v>69700</v>
+      </c>
+      <c r="J58" s="3">
         <v>71200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>70900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>69400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>69700</v>
-      </c>
-      <c r="M58" s="3">
-        <v>8100</v>
       </c>
       <c r="N58" s="3">
         <v>8100</v>
@@ -4584,7 +4718,7 @@
         <v>8100</v>
       </c>
       <c r="U58" s="3">
-        <v>8300</v>
+        <v>8100</v>
       </c>
       <c r="V58" s="3">
         <v>8300</v>
@@ -4592,8 +4726,8 @@
       <c r="W58" s="3">
         <v>8300</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
+      <c r="X58" s="3">
+        <v>8300</v>
       </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
@@ -4613,74 +4747,77 @@
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>13700</v>
+      </c>
+      <c r="E59" s="3">
         <v>14300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>12400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>12700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>19900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>129200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>183400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>205800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>169200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>146600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>200700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>190500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>136100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>114200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>157500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>119300</v>
       </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4699,74 +4836,77 @@
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>262000</v>
+      </c>
+      <c r="E60" s="3">
         <v>267600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>194000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>246900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>285900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>262100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>204600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>225800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>315300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>292400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>254600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>348000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>432900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>338200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>254200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>309700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>354100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>325800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>191600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>258200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>260700</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4785,74 +4925,77 @@
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>968900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1040800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>988500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>978300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>985400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1061000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>989100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>966500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>998900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1122100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>869100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>779700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>781300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>827900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>784500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>160000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>787700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>789300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>795400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1179600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1182800</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -4871,74 +5014,77 @@
       <c r="AD61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E62" s="3">
         <v>4100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>4600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>3100</v>
-      </c>
-      <c r="I62" s="3">
-        <v>3500</v>
       </c>
       <c r="J62" s="3">
         <v>3500</v>
       </c>
       <c r="K62" s="3">
-        <v>3100</v>
+        <v>3500</v>
       </c>
       <c r="L62" s="3">
         <v>3100</v>
       </c>
       <c r="M62" s="3">
+        <v>3100</v>
+      </c>
+      <c r="N62" s="3">
         <v>178700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>179900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>161500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>149800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>153800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>790000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>121700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>133200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>145300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>135700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>13600</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4957,8 +5103,11 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5043,8 +5192,11 @@
       <c r="AD63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5129,8 +5281,11 @@
       <c r="AD64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5215,74 +5370,77 @@
       <c r="AD65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1235700</v>
+      </c>
+      <c r="E66" s="3">
         <v>1312400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1187000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1227500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1273300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1326200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1197200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1195800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1317200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1418200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1302400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1307600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1375800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1315900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1192600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1259800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1263500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1248300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1132300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1573400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1457100</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5301,8 +5459,11 @@
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5333,8 +5494,9 @@
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
-    </row>
-    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5419,8 +5581,11 @@
       <c r="AD68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5505,8 +5670,11 @@
       <c r="AD69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5591,8 +5759,11 @@
       <c r="AD70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5677,74 +5848,77 @@
       <c r="AD71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-358400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-380100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-328800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-284200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-274300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-334900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-300400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-260800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-277300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-349900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-318300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-288100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-346000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-469000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-461500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-422500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-467000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-585800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-386600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-827200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-869200</v>
       </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5763,8 +5937,11 @@
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5849,8 +6026,11 @@
       <c r="AD73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5935,8 +6115,11 @@
       <c r="AD74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6021,74 +6204,77 @@
       <c r="AD75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-246200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-269500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-220000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-177100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-168200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-231000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-198600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-161400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-179800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-255000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-225600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-198000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-258800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-385700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-381300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-217600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-265700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-391000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-386400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-827000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-869100</v>
       </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6107,8 +6293,11 @@
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6193,174 +6382,180 @@
       <c r="AD77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45654</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45472</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45290</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45108</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45017</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44835</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44744</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44653</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44562</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44471</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44380</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44289</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44198</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44107</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44009</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43918</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43827</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43736</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43645</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43554</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43463</v>
       </c>
-      <c r="AD80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>21700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-51300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-44600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-9900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>60700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-34600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-39600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>16500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>72500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-31500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-30300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>57900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>123000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-14500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>44500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>118800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-30300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>42100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>71900</v>
       </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y81" s="3">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z81" s="3">
         <v>-26200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>800</v>
       </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
@@ -6370,8 +6565,11 @@
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6402,71 +6600,72 @@
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
-    </row>
-    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="E83" s="3">
         <v>6800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6900</v>
-      </c>
-      <c r="H83" s="3">
-        <v>7600</v>
       </c>
       <c r="I83" s="3">
         <v>7600</v>
       </c>
       <c r="J83" s="3">
+        <v>7600</v>
+      </c>
+      <c r="K83" s="3">
         <v>7000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>8500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7900</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>9200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>7300</v>
-      </c>
-      <c r="S83" s="3">
-        <v>6300</v>
       </c>
       <c r="T83" s="3">
         <v>6300</v>
       </c>
       <c r="U83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="V83" s="3">
         <v>6600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>8300</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6479,8 +6678,8 @@
       <c r="AA83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB83" s="3">
-        <v>0</v>
+      <c r="AB83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
@@ -6488,8 +6687,11 @@
       <c r="AD83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6574,8 +6776,11 @@
       <c r="AD84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6660,8 +6865,11 @@
       <c r="AD85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6746,8 +6954,11 @@
       <c r="AD86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6832,8 +7043,11 @@
       <c r="AD87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6918,71 +7132,74 @@
       <c r="AD88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>114900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-49200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-105100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>47100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>175500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-43200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-71900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>81300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>171200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-61600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-184400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-6000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>209400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-125600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>51200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>229800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>7800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-119300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>17500</v>
       </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
@@ -6995,8 +7212,8 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB89" s="3">
-        <v>0</v>
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC89" s="3">
         <v>0</v>
@@ -7004,8 +7221,11 @@
       <c r="AD89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7036,71 +7256,72 @@
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
-    </row>
-    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-12900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-6800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5100</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7113,8 +7334,8 @@
       <c r="AA91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB91" s="3">
-        <v>0</v>
+      <c r="AB91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC91" s="3">
         <v>0</v>
@@ -7122,8 +7343,11 @@
       <c r="AD91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7208,8 +7432,11 @@
       <c r="AD92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7294,71 +7521,74 @@
       <c r="AD93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-17300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-13700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-72800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-22300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-33400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-13200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-9100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-12800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5100</v>
       </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7371,8 +7601,8 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
@@ -7380,8 +7610,11 @@
       <c r="AD94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7412,8 +7645,9 @@
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
-    </row>
-    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7444,8 +7678,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7498,8 +7732,11 @@
       <c r="AD96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7584,8 +7821,11 @@
       <c r="AD97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7670,8 +7910,11 @@
       <c r="AD98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7756,71 +7999,74 @@
       <c r="AD99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-81700</v>
+      </c>
+      <c r="E100" s="3">
         <v>61300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>12800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-99200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>56500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>35500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-33700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-143100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>77400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>88600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-2000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-46000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>43200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-154100</v>
-      </c>
-      <c r="R100" s="3">
-        <v>-2000</v>
       </c>
       <c r="S100" s="3">
         <v>-2000</v>
       </c>
       <c r="T100" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="U100" s="3">
         <v>-8800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>66600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4200</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7833,8 +8079,8 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC100" s="3">
         <v>0</v>
@@ -7842,8 +8088,11 @@
       <c r="AD100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7874,8 +8123,8 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -7928,71 +8177,74 @@
       <c r="AD101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
+      <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>25400</v>
+      </c>
+      <c r="E102" s="3">
         <v>5600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-96900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>34100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>66000</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-47000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>36000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>6000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-109600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-80800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>141200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-290200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>36000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>218700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-13700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-53000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>8200</v>
       </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8005,13 +8257,16 @@
       <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB102" s="3">
-        <v>0</v>
+      <c r="AB102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC102" s="3">
         <v>0</v>
       </c>
       <c r="AD102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE102" s="3">
         <v>0</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/LESL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LESL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="92">
   <si>
     <t>LESL</t>
   </si>
@@ -656,398 +656,423 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46025</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45934</v>
+      </c>
+      <c r="F7" s="2">
         <v>45836</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45745</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45654</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45563</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45472</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45381</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45290</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45108</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45017</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44835</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44744</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44653</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44562</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44471</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44380</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>44289</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>44198</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>44107</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>44009</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>43918</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>43827</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>43736</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>43645</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>43554</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AF7" s="2">
         <v>43463</v>
       </c>
-      <c r="AE7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>147100</v>
+      </c>
+      <c r="E8" s="3">
+        <v>389200</v>
+      </c>
+      <c r="F8" s="3">
         <v>500300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>177100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>175200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>397900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>569600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>188700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>174000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>432400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>610900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>212800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>195100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>475600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>673600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>228100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>184800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>408900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>596500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>192400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>145000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>381300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>479900</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB8" s="3">
         <v>123000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>298200</v>
       </c>
-      <c r="AB8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>120100</v>
+      </c>
+      <c r="E9" s="3">
+        <v>239100</v>
+      </c>
+      <c r="F9" s="3">
         <v>302500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>133200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>127500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>254600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>340800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>134300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>123600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>272200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>359300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>141700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>129800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>258400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>370000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>142400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>117500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>220900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>312800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>120800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>93300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>214700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>269200</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB9" s="3">
         <v>81900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>166900</v>
       </c>
-      <c r="AB9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E10" s="3">
+        <v>150100</v>
+      </c>
+      <c r="F10" s="3">
         <v>197900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>43900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>47700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>143200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>228800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>54300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>50400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>160200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>251600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>71200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>65300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>217200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>303600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>85700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>67300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>188000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>283700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>71600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>51700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>166600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>210700</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB10" s="3">
         <v>41100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>131300</v>
       </c>
-      <c r="AB10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1079,8 +1104,10 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1168,8 +1195,14 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1257,50 +1290,56 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>13100</v>
+      </c>
+      <c r="E14" s="3">
+        <v>185900</v>
+      </c>
+      <c r="F14" s="3">
         <v>3100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>2100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>6900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>1300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>1000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="M14" s="3">
         <v>9700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="N14" s="3">
         <v>2300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>4200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>3500</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
@@ -1308,85 +1347,91 @@
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>6400</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>1900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>7300</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>2300</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E15" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F15" s="3">
         <v>8600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>8300</v>
-      </c>
-      <c r="F15" s="3">
-        <v>8200</v>
-      </c>
-      <c r="G15" s="3">
-        <v>8700</v>
       </c>
       <c r="H15" s="3">
         <v>8200</v>
       </c>
       <c r="I15" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J15" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K15" s="3">
         <v>7800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>8300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>8600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>8100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>8900</v>
       </c>
-      <c r="N15" s="3">
-        <v>0</v>
-      </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1435,8 +1480,14 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1465,186 +1516,200 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>202700</v>
+      </c>
+      <c r="E17" s="3">
+        <v>353400</v>
+      </c>
+      <c r="F17" s="3">
         <v>428900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>223400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>214500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>364500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>470700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>218500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>209400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>384100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>492800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>233900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>222100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>392500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>501500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>232100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>197300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>341800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>430100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>193000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>178100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>313300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>368300</v>
       </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB17" s="3">
         <v>141600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>239300</v>
       </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-55600</v>
+      </c>
+      <c r="E18" s="3">
+        <v>35800</v>
+      </c>
+      <c r="F18" s="3">
         <v>71400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-46300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-39300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>33300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>99000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-29800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-35500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>48300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>118100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>-21000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>-27000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>83100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>172100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>-4000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>-12500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>67100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>166400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>-600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>-33100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>68000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>111600</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB18" s="3">
         <v>-18600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>58900</v>
       </c>
-      <c r="AB18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1676,8 +1741,10 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1711,418 +1778,448 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3">
-        <v>0</v>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-1000</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-600</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-47800</v>
+      </c>
+      <c r="E21" s="3">
+        <v>44200</v>
+      </c>
+      <c r="F21" s="3">
         <v>80000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-38000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-31100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>42000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>107200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-22000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-27100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>56900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>126300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>-12100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>-18500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>91000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>179300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>2400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>-3600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>74000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>171900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>4600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>-26500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>76200</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC21" s="3">
         <v>86300</v>
       </c>
-      <c r="AB21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>15800</v>
+        <v>13500</v>
       </c>
       <c r="E22" s="3">
-        <v>15900</v>
+        <v>15500</v>
       </c>
       <c r="F22" s="3">
         <v>15800</v>
       </c>
       <c r="G22" s="3">
+        <v>15900</v>
+      </c>
+      <c r="H22" s="3">
+        <v>15800</v>
+      </c>
+      <c r="I22" s="3">
         <v>17000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>18200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>18200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>17100</v>
-      </c>
-      <c r="K22" s="3">
-        <v>17200</v>
-      </c>
-      <c r="L22" s="3">
-        <v>17700</v>
       </c>
       <c r="M22" s="3">
         <v>17200</v>
       </c>
       <c r="N22" s="3">
+        <v>17700</v>
+      </c>
+      <c r="O22" s="3">
+        <v>17200</v>
+      </c>
+      <c r="P22" s="3">
         <v>13400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>9600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>6800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>6900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>6900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>7400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>7400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>8100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>11500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>18600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>19500</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB22" s="3">
         <v>22400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>23900</v>
       </c>
-      <c r="AB22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-82300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-165600</v>
+      </c>
+      <c r="F23" s="3">
         <v>52600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-64300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-55500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>9400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>79500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-48700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-53500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>21400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>98100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>-42400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>-40300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>73500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>165400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>-11100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>-19700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>59300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>158200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>-9800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>-44600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>49300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>91500</v>
       </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB23" s="3">
         <v>-41200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>32000</v>
       </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>700</v>
+      </c>
+      <c r="E24" s="3">
+        <v>-2800</v>
+      </c>
+      <c r="F24" s="3">
         <v>30800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>-13000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>-10900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>19300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>18900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>-14100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>-14000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>4900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>25600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-10900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>-10100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>15600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>42400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-3700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-5300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>14700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>39400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-3300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>-14300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>7200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>19600</v>
       </c>
-      <c r="Y24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB24" s="3">
         <v>-15000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>31200</v>
       </c>
-      <c r="AB24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2210,186 +2307,204 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-83000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-162800</v>
+      </c>
+      <c r="F26" s="3">
         <v>21700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-51300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-44600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-9900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>60700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-34600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-39600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>16500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>72500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>-31500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>-30300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>57900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>123000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>-7400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>-14500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>44500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>118800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>-6500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>-30300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>42100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>71900</v>
       </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-26200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>800</v>
       </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-83000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-162800</v>
+      </c>
+      <c r="F27" s="3">
         <v>21700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-51300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-44600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-9900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>60700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-34600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-39600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>16500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>72500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>-31500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>-30300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>57900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>123000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>-7400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>-14500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>44500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>118800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>-6500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>-30300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>42100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>71900</v>
       </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB27" s="3">
         <v>-26200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>800</v>
       </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2477,8 +2592,14 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2566,8 +2687,14 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2655,8 +2782,14 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2744,8 +2877,14 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2779,151 +2918,163 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
-      <c r="O32" s="3">
-        <v>0</v>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>1000</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
         <v>200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>600</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB32" s="3">
         <v>200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>3000</v>
       </c>
-      <c r="AB32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-83000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-162800</v>
+      </c>
+      <c r="F33" s="3">
         <v>21700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-51300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-44600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-9900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>60700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-34600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-39600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>16500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>72500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-31500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>-30300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>57900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>123000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-7400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>-14500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>44500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>118800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>-6500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>-30300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>42100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>71900</v>
       </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB33" s="3">
         <v>-26200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>800</v>
       </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3011,191 +3162,209 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-83000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-162800</v>
+      </c>
+      <c r="F35" s="3">
         <v>21700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-51300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-44600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-9900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>60700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-34600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-39600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>16500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>72500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-31500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>-30300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>57900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>123000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-7400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>-14500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>44500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>118800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>-6500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>-30300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>42100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>71900</v>
       </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB35" s="3">
         <v>-26200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>800</v>
       </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46025</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45934</v>
+      </c>
+      <c r="F38" s="2">
         <v>45836</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45745</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45654</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45563</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45472</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45381</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45290</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45108</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45017</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44835</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44744</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44653</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44562</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44471</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44380</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>44289</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>44198</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>44107</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>44009</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>43918</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>43827</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>43736</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>43645</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>43554</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AF38" s="2">
         <v>43463</v>
       </c>
-      <c r="AE38" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3227,8 +3396,10 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3260,80 +3431,82 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E41" s="3">
+        <v>64300</v>
+      </c>
+      <c r="F41" s="3">
         <v>42700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>17300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>11600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>108500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>74400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>8400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>8400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>55400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>19400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>8700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>2700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>112300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>193100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>52000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>53300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>343500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>309100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>88700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>102800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>157100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>148900</v>
       </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3522,14 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3438,80 +3617,86 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>26500</v>
+      </c>
+      <c r="F43" s="3">
         <v>34800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>32000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>29800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>45500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>48200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>34400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>22500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>29400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>49300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>60400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>46400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>45300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>47300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>44200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>39400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>77700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>47800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>94500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>74200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>31500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>35800</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3527,80 +3712,86 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>210000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>208000</v>
+      </c>
+      <c r="F44" s="3">
         <v>273200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>335100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>271100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>234300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>302200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>379100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>334000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>311800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>436600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>492300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>429500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>361700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>361400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>345000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>244600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>198800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>224500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>277900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>174500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>149000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>181100</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3616,80 +3807,86 @@
       <c r="AE44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>10900</v>
+      </c>
+      <c r="F45" s="3">
         <v>12900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>13500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>9600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>9400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>9100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>13000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>12000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>5900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>13900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>15300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>29900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>23100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>30500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>30700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>38200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>41100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>28600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>87300</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>65500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>22700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>24600</v>
       </c>
-      <c r="Y45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3705,80 +3902,86 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>267000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>328800</v>
+      </c>
+      <c r="F46" s="3">
         <v>385100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>417600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>341600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>422400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>457000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>453600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>392000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>420300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>536700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>591700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>508500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>542400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>632300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>471900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>375500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>601700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>610100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>448300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>340100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>360200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>390400</v>
       </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
@@ -3794,8 +3997,14 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3829,11 +4038,11 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
-      </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -3883,80 +4092,86 @@
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>316400</v>
+      </c>
+      <c r="E48" s="3">
+        <v>345500</v>
+      </c>
+      <c r="F48" s="3">
         <v>355100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>346400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>356900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>368900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>376700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>350000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>330700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>341700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>335800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>312000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>308900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>314600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>293300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>279100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>273200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>282600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>235400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>245200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>253800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>244000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>74700</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3972,80 +4187,86 @@
       <c r="AE48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>30700</v>
+      </c>
+      <c r="F49" s="3">
         <v>212400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>213300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>214200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>215100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>216000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>217000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>217900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>218900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>219800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>216600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>218100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>213700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>155700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>146900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>132400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>129000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>127700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>128600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>121200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>122000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>121700</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4061,8 +4282,14 @@
       <c r="AE49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4150,8 +4377,14 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4239,80 +4472,86 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E52" s="3">
+        <v>36400</v>
+      </c>
+      <c r="F52" s="3">
         <v>36900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>36500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>38200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>39700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>40000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>40300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>41900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>46000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>44900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>42900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>41300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>39000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>35700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>32400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>30200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>28900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>24600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>35900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>31400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>21000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1200</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4328,8 +4567,14 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4417,80 +4662,86 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>649400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>741500</v>
+      </c>
+      <c r="F54" s="3">
         <v>989500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1043000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>967000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1050300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1105200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1095200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>998500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1034400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1137400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1163200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1076800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1109600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1117000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>930200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>811300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>1042200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>997800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>857300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>745800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>746400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>588000</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4506,8 +4757,14 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4539,8 +4796,10 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4572,80 +4831,82 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>45200</v>
+      </c>
+      <c r="E57" s="3">
+        <v>51900</v>
+      </c>
+      <c r="F57" s="3">
         <v>91600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>114800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>56200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>67600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>108900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>112400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>63500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>58600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>147400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>139800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>117300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>156500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>219000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>160900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>99500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>101000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>155500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>181500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>69000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>92400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>133100</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
@@ -4661,46 +4922,52 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>73900</v>
+      </c>
+      <c r="E58" s="3">
+        <v>75000</v>
+      </c>
+      <c r="F58" s="3">
         <v>65800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>64500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>65100</v>
       </c>
-      <c r="G58" s="3">
-        <v>71800</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
+        <v>71500</v>
+      </c>
+      <c r="J58" s="3">
         <v>69700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>69700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>71200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>70900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>69400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>69700</v>
-      </c>
-      <c r="N58" s="3">
-        <v>8100</v>
-      </c>
-      <c r="O58" s="3">
-        <v>8100</v>
       </c>
       <c r="P58" s="3">
         <v>8100</v>
@@ -4721,19 +4988,19 @@
         <v>8100</v>
       </c>
       <c r="V58" s="3">
-        <v>8300</v>
+        <v>8100</v>
       </c>
       <c r="W58" s="3">
-        <v>8300</v>
+        <v>8100</v>
       </c>
       <c r="X58" s="3">
         <v>8300</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z58" s="3" t="s">
-        <v>3</v>
+      <c r="Y58" s="3">
+        <v>8300</v>
+      </c>
+      <c r="Z58" s="3">
+        <v>8300</v>
       </c>
       <c r="AA58" s="3" t="s">
         <v>3</v>
@@ -4750,80 +5017,86 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E59" s="3">
+        <v>13600</v>
+      </c>
+      <c r="F59" s="3">
         <v>13700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>14300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>12400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>12700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>12100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>13900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>11800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>19900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>16800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>15100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>129200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>183400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>205800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>169200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>146600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>200700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>190500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>136100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>114200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>157500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>119300</v>
       </c>
-      <c r="Y59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
@@ -4839,80 +5112,86 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>188000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>209100</v>
+      </c>
+      <c r="F60" s="3">
         <v>262000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>267600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>194000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>246900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>285900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>262100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>204600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>225800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>315300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>292400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>254600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>348000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>432900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>338200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>254200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>309700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>354100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>325800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>191600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>258200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>260700</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
@@ -4928,80 +5207,86 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>948000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>938200</v>
+      </c>
+      <c r="F61" s="3">
         <v>968900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1040800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>988500</v>
       </c>
-      <c r="G61" s="3">
-        <v>978300</v>
-      </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
+        <v>978100</v>
+      </c>
+      <c r="J61" s="3">
         <v>985400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1061000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>989100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>966500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>998900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1122100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>869100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>779700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>781300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>827900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>784500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>160000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>787700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>789300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>795400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1179600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>1182800</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>0</v>
-      </c>
       <c r="AA61" s="3">
         <v>0</v>
       </c>
@@ -5017,80 +5302,86 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>2000</v>
+      </c>
+      <c r="F62" s="3">
         <v>3200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>4100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>4600</v>
       </c>
-      <c r="G62" s="3">
-        <v>2300</v>
-      </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
+        <v>2400</v>
+      </c>
+      <c r="J62" s="3">
         <v>2100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>3100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>3500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>3500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>3100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>3100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>178700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>179900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>161500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>149800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>153800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>790000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>121700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>133200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>145300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>135700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>13600</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5106,8 +5397,14 @@
       <c r="AE62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5195,8 +5492,14 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5284,8 +5587,14 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5373,80 +5682,86 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1139300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>1149500</v>
+      </c>
+      <c r="F66" s="3">
         <v>1235700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>1312400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>1187000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>1227500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>1273300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>1326200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>1197200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>1195800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>1317200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>1418200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>1302400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>1307600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>1375800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>1315900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>1192600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>1259800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>1263500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>1248300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>1132300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>1573400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>1457100</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5462,8 +5777,14 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5495,8 +5816,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5584,8 +5907,14 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5673,8 +6002,14 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5762,8 +6097,14 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5851,80 +6192,86 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-604100</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-521200</v>
+      </c>
+      <c r="F72" s="3">
         <v>-358400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-380100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-328800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-284200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-274300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-334900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-300400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-260800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-277300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-349900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-318300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-288100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-346000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>-469000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>-461500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>-422500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>-467000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>-585800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>-386600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>-827200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>-869200</v>
       </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
@@ -5940,8 +6287,14 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6029,8 +6382,14 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6118,8 +6477,14 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6207,80 +6572,86 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-489900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-408000</v>
+      </c>
+      <c r="F76" s="3">
         <v>-246200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>-269500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>-220000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>-177100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>-168200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>-231000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>-198600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>-161400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>-179800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>-255000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>-225600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>-198000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>-258800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>-385700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>-381300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>-217600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>-265700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>-391000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>-386400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>-827000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>-869100</v>
       </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6296,8 +6667,14 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6385,191 +6762,209 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46025</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45934</v>
+      </c>
+      <c r="F80" s="2">
         <v>45836</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45745</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45654</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45563</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45472</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45381</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45290</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45108</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45017</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44835</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44744</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44653</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44562</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44471</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44380</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>44289</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>44198</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>44107</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>44009</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>43918</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>43827</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>43736</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>43645</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>43554</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AF80" s="2">
         <v>43463</v>
       </c>
-      <c r="AE80" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-83000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-162800</v>
+      </c>
+      <c r="F81" s="3">
         <v>21700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-51300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-44600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-9900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>60700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-34600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-39600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>16500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>72500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-31500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>-30300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>57900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>123000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-7400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>-14500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>44500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>118800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>-6500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>-30300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>42100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>71900</v>
       </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB81" s="3">
         <v>-26200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>800</v>
       </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="AC81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6601,8 +6996,10 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -6610,68 +7007,68 @@
         <v>7300</v>
       </c>
       <c r="E83" s="3">
+        <v>7800</v>
+      </c>
+      <c r="F83" s="3">
+        <v>7300</v>
+      </c>
+      <c r="G83" s="3">
         <v>6800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>7400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>7700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>6900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>7600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>7600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>7000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>6400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>6500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>8500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>7900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>7100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>6600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>9200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>7300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>6300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>6300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>6600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>8300</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6681,17 +7078,23 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>0</v>
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6779,8 +7182,14 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6868,8 +7277,14 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6957,8 +7372,14 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7046,8 +7467,14 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7135,77 +7562,83 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-81100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>48200</v>
+      </c>
+      <c r="F89" s="3">
         <v>114900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-49200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-105100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>47100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>175500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-43200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-71900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>81300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>171200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-61600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-184400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-6000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>209400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-11200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-125600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>51200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>229800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>7800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-119300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>17500</v>
       </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
@@ -7215,17 +7648,23 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD89" s="3">
-        <v>0</v>
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7257,77 +7696,79 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="F91" s="3">
         <v>-7900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-6500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-4700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-12900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-10300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-13300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-10700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-11800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-11900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-9100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-5700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-5800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-8900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-5400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-11100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-8300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-6800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-2700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-5100</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7337,17 +7778,23 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7435,8 +7882,14 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7524,77 +7977,83 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-6400</v>
+      </c>
+      <c r="F94" s="3">
         <v>-7800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-6500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-4600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-12900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-10300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-13300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-10700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-11600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-17300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-9800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-13700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-72800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-22300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-33400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-10500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-13200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-9100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-12800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-5100</v>
       </c>
-      <c r="X94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
@@ -7604,17 +8063,23 @@
       <c r="AB94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC94" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>0</v>
+      <c r="AC94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7646,8 +8111,10 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7681,11 +8148,11 @@
       <c r="M96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N96" s="3">
-        <v>0</v>
-      </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7735,8 +8202,14 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7824,8 +8297,14 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7913,8 +8392,14 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8002,77 +8487,83 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-20200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-81700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>61300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>12800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-99200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>56500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>35500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-33700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-143100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>77400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>88600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-2000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-46000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>43200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-154100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-2000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-2000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-8800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>66600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-4200</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8082,17 +8573,23 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD100" s="3">
-        <v>0</v>
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8126,11 +8623,11 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -8180,77 +8677,83 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-60700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>21700</v>
+      </c>
+      <c r="F102" s="3">
         <v>25400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>5600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-96900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>34100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>66000</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-47000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>36000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>10700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>6000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-109600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-80800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>141200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-1400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-290200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>36000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>218700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-13700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-53000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>8200</v>
       </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
@@ -8260,13 +8763,19 @@
       <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD102" s="3">
-        <v>0</v>
+      <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF102" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG102" s="3">
         <v>0</v>
       </c>
     </row>
